--- a/AutosurveillanceTemplates/Comparatif.xlsx
+++ b/AutosurveillanceTemplates/Comparatif.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4895F7-CB2D-4156-9901-40E0E8D5A377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34A16B1-30EE-496B-8C59-FAFC8ED3D4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="777" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-8205" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comparatif" sheetId="137" r:id="rId1"/>
-    <sheet name="LimitequantificationSDE" sheetId="9" r:id="rId2"/>
-    <sheet name="SeuilsComparaison-EMT" sheetId="8" r:id="rId3"/>
+    <sheet name="SeuilsComparaison-EMT" sheetId="8" r:id="rId2"/>
+    <sheet name="LimitequantificationSDE" sheetId="9" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,34 +35,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={B4132B75-E79F-4C91-84CF-E3DED874F9F6}</author>
-  </authors>
-  <commentList>
-    <comment ref="J27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1700-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color theme="1"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Commentaire à thread]
-Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
-Commentaire :
-    En attente du retour de RMC si % ou mg/l</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="90">
   <si>
     <t>Code SANDRE</t>
   </si>
@@ -342,44 +316,65 @@
     <t>en g/l</t>
   </si>
   <si>
-    <t>si S4</t>
-  </si>
-  <si>
     <t>COMMENTAIRES :</t>
   </si>
   <si>
-    <t>Informations sur le comparatif</t>
-  </si>
-  <si>
-    <t>Préleveur :</t>
-  </si>
-  <si>
-    <t>Date du comparatif :</t>
-  </si>
-  <si>
-    <t>Nom de la station :</t>
-  </si>
-  <si>
-    <t>Code de la station :</t>
-  </si>
-  <si>
-    <t>Résultats du comparatif</t>
-  </si>
-  <si>
-    <t>Laboratoire du MO/exploitant</t>
-  </si>
-  <si>
-    <t>Laboratoire de contrôle</t>
-  </si>
-  <si>
-    <t>NB analyses</t>
-  </si>
-  <si>
-    <t>Le comparatif est-il effectué à partir des prélévements d'une autre station ? 
-(si oui, précisez la station)</t>
-  </si>
-  <si>
-    <t>NB conformes</t>
+    <t xml:space="preserve">Préleveur : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date du comparatif : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le comparatif est-il effectué à partir des prélévements d'une autre station ? </t>
+  </si>
+  <si>
+    <t>EMT</t>
+  </si>
+  <si>
+    <t>Nombre d'analyses
+réalisées</t>
+  </si>
+  <si>
+    <t>Nombre d'analyses
+conformes</t>
+  </si>
+  <si>
+    <t>Coefficient Analytique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans l'affirmative, préciser la station : </t>
+  </si>
+  <si>
+    <t>Informations sur le comparatif analytique</t>
+  </si>
+  <si>
+    <t>Résultats du comparatif analytique</t>
+  </si>
+  <si>
+    <t>Laboratoire du
+Maître d'Ouvrage/exploitant</t>
+  </si>
+  <si>
+    <t>Laboratoire de
+contrôle</t>
+  </si>
+  <si>
+    <t>Les analyses sont-elles correctement effectuées ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nom du(des) laboratoire(s) réalisant les analyses de la matrice eau : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nom du(des) laboratoire(s) réalisant l'analyse de la siccité des boues et des matières séches : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le(s) laboratoire(s) est/sont-il(s) agréé(s) au titre du code de l’environnement pour l'ensemble des paramètres de la matrice eau résiduaire ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A défaut, est ce que le laboratoire réalise un exercice concluant d’intercalibration avec un laboratoire agréé ? </t>
+  </si>
+  <si>
+    <t>non prise en compte</t>
   </si>
 </sst>
 </file>
@@ -389,12 +384,26 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -514,22 +523,43 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="0"/>
+      <sz val="10"/>
+      <color theme="2"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0"/>
+      <i/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -586,12 +616,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFB896EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EEFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="64">
+  <borders count="62">
     <border>
       <left/>
       <right/>
@@ -794,6 +842,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -1067,6 +1135,48 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1076,11 +1186,18 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="hair">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="hair">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1169,7 +1286,24 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="hair">
         <color indexed="64"/>
       </top>
@@ -1177,85 +1311,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="hair">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <top/>
+      <bottom style="hair">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1263,21 +1328,6 @@
         <color indexed="64"/>
       </left>
       <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1287,36 +1337,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1328,564 +1363,721 @@
     <border>
       <left style="hair">
         <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="3"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="3"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="3"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="3"/>
-      </right>
-      <top style="thin">
-        <color theme="3"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="3"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="3"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="3"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color theme="3"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
-        <color theme="3"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="3"/>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="3"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="9" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="14" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="17" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="7" borderId="19" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="7" borderId="27" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="7" borderId="29" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="7" borderId="33" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="7" borderId="29" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="7" borderId="31" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="7" borderId="35" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="38" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="7" borderId="39" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="7" borderId="46" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="7" borderId="23" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="7" borderId="25" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="8" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="8" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="8" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="8" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="13" borderId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="13" borderId="42" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -1899,117 +2091,206 @@
     <cellStyle name="Normal 6" xfId="6" xr:uid="{A19F0B02-47E9-4D2C-B3F6-A8C99D86DDDE}"/>
     <cellStyle name="Pourcentage 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="9">
     <dxf>
       <font>
-        <color auto="1"/>
-      </font>
-      <border>
-        <left style="hair">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor rgb="FFD57A44"/>
         </patternFill>
       </fill>
       <border>
         <left style="thin">
           <color auto="1"/>
         </left>
-        <right style="hair">
+        <right style="thin">
           <color auto="1"/>
         </right>
-        <top style="thin">
+        <top style="hair">
           <color auto="1"/>
         </top>
-        <bottom style="thin">
+        <bottom style="hair">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
       <font>
-        <color auto="1"/>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
+          <bgColor rgb="FF7AB51C"/>
         </patternFill>
       </fill>
       <border>
         <left style="thin">
           <color auto="1"/>
         </left>
-        <right style="hair">
+        <right style="thin">
           <color auto="1"/>
         </right>
-        <top style="thin">
+        <top style="hair">
           <color auto="1"/>
         </top>
-        <bottom style="thin">
+        <bottom style="hair">
           <color auto="1"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="hair">
+          <color auto="1"/>
+        </top>
+        <bottom style="hair">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="hair">
+          <color auto="1"/>
+        </top>
+        <bottom style="hair">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EEFF" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD57A44"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7AB51C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="mediumGray"/>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF76B82A"/>
-      <color rgb="FF002DE0"/>
-      <color rgb="FF00E0B3"/>
-      <color rgb="FF009DE0"/>
-      <color rgb="FF009FE3"/>
-      <color rgb="FF008080"/>
-      <color rgb="FF00B0AC"/>
-      <color rgb="FFFFFFB9"/>
-      <color rgb="FF006699"/>
-      <color rgb="FFD9FFFF"/>
+      <color rgb="FFD57A44"/>
+      <color rgb="FF7AB51C"/>
+      <color rgb="FFFFC7CE"/>
+      <color rgb="FF9C0006"/>
+      <color rgb="FFC6EFCE"/>
+      <color rgb="FF1F497D"/>
+      <color rgb="FFE6DC8F"/>
+      <color rgb="FF81421D"/>
+      <color rgb="FFFF9966"/>
+      <color rgb="FFA50021"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2021,12 +2302,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="PELLETIER Clémentine" id="{5FA9D90E-9B90-4400-BDE0-D953E751ACC4}" userId="S::Clementine.PELLETIER@eau-loire-bretagne.fr::00f649e6-0a0a-4289-a39b-586495493301" providerId="AD"/>
-</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2314,863 +2589,1066 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J25" dT="2023-11-24T10:15:44.48" personId="{5FA9D90E-9B90-4400-BDE0-D953E751ACC4}" id="{B4132B75-E79F-4C91-84CF-E3DED874F9F6}">
-    <text>En attente du retour de RMC si % ou mg/l</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B67ED775-84A5-4DBA-AC81-69F58B98E90C}">
   <sheetPr codeName="Feuil27">
     <tabColor theme="3" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.703125" defaultRowHeight="13" outlineLevelRow="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="15" width="10.703125" style="66"/>
+    <col min="1" max="13" width="12.703125" style="66" customWidth="1"/>
+    <col min="14" max="14" width="12.703125" style="72" customWidth="1"/>
+    <col min="15" max="15" width="15.64453125" style="72" customWidth="1"/>
     <col min="16" max="16" width="2.703125" style="66" customWidth="1"/>
-    <col min="17" max="17" width="2.703125" style="67" customWidth="1"/>
-    <col min="18" max="19" width="10.703125" style="67" customWidth="1"/>
-    <col min="20" max="23" width="10.703125" style="67"/>
-    <col min="24" max="16384" width="10.703125" style="66"/>
+    <col min="17" max="17" width="2.703125" style="65" customWidth="1"/>
+    <col min="18" max="19" width="10.703125" style="65" customWidth="1"/>
+    <col min="20" max="29" width="10.703125" style="65"/>
+    <col min="30" max="16384" width="10.703125" style="66"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="130" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="68"/>
+    </row>
+    <row r="2" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="142" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="143"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="147"/>
+      <c r="H2" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="70"/>
-      <c r="P1" s="71"/>
-    </row>
-    <row r="2" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="93" t="s">
+      <c r="I2" s="143"/>
+      <c r="J2" s="148"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="68"/>
+    </row>
+    <row r="3" spans="1:20" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="107" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="93" t="s">
-        <v>75</v>
-      </c>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="95"/>
-      <c r="L2" s="95"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="96"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="71"/>
-    </row>
-    <row r="3" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="79" t="s">
+      <c r="B3" s="108"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="149" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="150"/>
+      <c r="J3" s="151"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="134"/>
+      <c r="M3" s="134"/>
+      <c r="N3" s="134"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="68"/>
+    </row>
+    <row r="4" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="68"/>
+    </row>
+    <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
+      <c r="L5" s="98"/>
+      <c r="M5" s="98"/>
+      <c r="N5" s="98"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="68"/>
+    </row>
+    <row r="6" spans="1:20" ht="19.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="92"/>
+      <c r="L6" s="92"/>
+      <c r="M6" s="92"/>
+      <c r="N6" s="93"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="68"/>
+    </row>
+    <row r="7" spans="1:20" ht="19.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="99" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="93"/>
+      <c r="O7" s="76"/>
+      <c r="P7" s="68"/>
+    </row>
+    <row r="8" spans="1:20" ht="30.7" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="90" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="91"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="92"/>
+      <c r="L8" s="92"/>
+      <c r="M8" s="92"/>
+      <c r="N8" s="93"/>
+      <c r="O8" s="76"/>
+      <c r="P8" s="68"/>
+    </row>
+    <row r="9" spans="1:20" ht="32" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="94" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="95"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="97"/>
+      <c r="O9" s="76"/>
+      <c r="P9" s="68"/>
+    </row>
+    <row r="10" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="77"/>
+      <c r="O10" s="76"/>
+      <c r="P10" s="68"/>
+    </row>
+    <row r="11" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="110" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="111"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="111"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="111"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="111"/>
+      <c r="L11" s="111"/>
+      <c r="M11" s="111"/>
+      <c r="N11" s="112"/>
+      <c r="O11" s="76"/>
+      <c r="P11" s="68"/>
+    </row>
+    <row r="12" spans="1:20" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="126" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="126"/>
+      <c r="C12" s="127" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="87" t="s">
+      <c r="E12" s="127"/>
+      <c r="F12" s="126" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="127" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="127"/>
+      <c r="I12" s="126" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="I3" s="88"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="89"/>
-      <c r="L3" s="89"/>
-      <c r="M3" s="89"/>
-      <c r="N3" s="89"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="71"/>
-    </row>
-    <row r="4" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="87" t="s">
+      <c r="K12" s="129"/>
+      <c r="L12" s="128" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="88"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="89"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="89"/>
-      <c r="N4" s="89"/>
-      <c r="O4" s="70"/>
-      <c r="P4" s="71"/>
-    </row>
-    <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="70"/>
-      <c r="P5" s="71"/>
-    </row>
-    <row r="6" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="90" t="s">
+      <c r="M12" s="129"/>
+      <c r="N12" s="78" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="91"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="91"/>
-      <c r="E6" s="91"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="91"/>
-      <c r="M6" s="91"/>
-      <c r="N6" s="78"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="71"/>
-    </row>
-    <row r="7" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="101" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="101"/>
-      <c r="C7" s="102" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="102" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" s="102"/>
-      <c r="F7" s="101" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="102" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="102"/>
-      <c r="I7" s="101" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="103" t="s">
-        <v>81</v>
-      </c>
-      <c r="K7" s="103"/>
-      <c r="L7" s="103" t="s">
-        <v>83</v>
-      </c>
-      <c r="M7" s="103"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="70"/>
-      <c r="P7" s="71"/>
-    </row>
-    <row r="8" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="101"/>
-      <c r="B8" s="101"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="101"/>
-      <c r="J8" s="104">
-        <f>COUNT(D10:E21)</f>
+      <c r="O12" s="76"/>
+      <c r="P12" s="68"/>
+    </row>
+    <row r="13" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="126"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="126"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="122">
+        <f>COUNTA(D15:E24)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="104"/>
-      <c r="L8" s="104">
-        <f>COUNTIF(L10:M21,"=oui")</f>
+      <c r="K13" s="123"/>
+      <c r="L13" s="122">
+        <f>COUNTIF(L15:M24,"=Oui")</f>
         <v>0</v>
       </c>
-      <c r="M8" s="104"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="70"/>
-      <c r="P8" s="71"/>
-      <c r="Q8" s="67" t="str">
+      <c r="M13" s="123"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="76"/>
+      <c r="P13" s="68"/>
+      <c r="Q13" s="65" t="str">
         <f>IF(D2&lt;&gt;"",D2,"")</f>
         <v/>
       </c>
-      <c r="R8" s="67" t="str">
-        <f>IF(Q8&lt;&gt;"",J8,"")</f>
+      <c r="R13" s="65" t="str">
+        <f>IF(Q13&lt;&gt;"",J13,"")</f>
         <v/>
       </c>
-      <c r="S8" s="67" t="str">
-        <f>IF(Q8&lt;&gt;"",L8,"")</f>
+      <c r="S13" s="65" t="str">
+        <f>IF(Q13&lt;&gt;"",L13,"")</f>
         <v/>
       </c>
-      <c r="T8" s="67" t="str">
-        <f>IF(J8&gt;0,100*(L8/J8),"")</f>
+      <c r="T13" s="65" t="str">
+        <f>IF(J13&gt;0,100*(L13/J13),"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="101"/>
-      <c r="B9" s="101"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="102"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="103" t="s">
+    <row r="14" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="126"/>
+      <c r="B14" s="126"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="K9" s="103"/>
-      <c r="L9" s="103" t="s">
+      <c r="K14" s="125"/>
+      <c r="L14" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="M9" s="103"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="71"/>
-    </row>
-    <row r="10" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="97" t="s">
+      <c r="M14" s="125"/>
+      <c r="N14" s="79" t="s">
+        <v>75</v>
+      </c>
+      <c r="O14" s="76"/>
+      <c r="P14" s="68"/>
+    </row>
+    <row r="15" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="153" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="97"/>
-      <c r="C10" s="75">
-        <f>VLOOKUP(A10, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
+      <c r="B15" s="153"/>
+      <c r="C15" s="71">
+        <f>VLOOKUP(A15, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>3</v>
       </c>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="99" t="str">
-        <f>IF(OR(G10="",D10=""),"",IF(ISERROR(VLOOKUP(A10,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G10)=TRUE,SUBSTITUTE(G10,"&lt;","",1)*1,G10)&gt;VLOOKUP(A10,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D10)=TRUE,SUBSTITUTE(D10,"&lt;","",1)*1,D10)&gt;VLOOKUP(A10,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D10)=TRUE,SUBSTITUTE(D10,"&lt;","",1)*1,D10)-((IF(ISTEXT(D10)=TRUE,SUBSTITUTE(D10,"&lt;","",1)*1,D10)+IF(ISTEXT(G10)=TRUE,SUBSTITUTE(G10,"&lt;","",1)*1,G10))/2))/((IF(ISTEXT(D10)=TRUE,SUBSTITUTE(D10,"&lt;","",1)*1,D10)+IF(ISTEXT(G10)=TRUE,SUBSTITUTE(G10,"&lt;","",1),G10))/2),"-")))</f>
-        <v/>
-      </c>
-      <c r="K10" s="99"/>
-      <c r="L10" s="100" t="str">
-        <f>IF(OR(D10="",G10=""),"",IF(AND(F10="Oui",I10="Oui"),"Oui",IF(J10="-","Oui",IF(OR(G10&gt;VLOOKUP($D10,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D10&gt;VLOOKUP($D10,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G10&lt;=VLOOKUP($D10,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J10)&lt;=VLOOKUP($D10,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J10)&lt;=VLOOKUP($D10,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
-        <v/>
-      </c>
-      <c r="M10" s="100"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="70"/>
-      <c r="P10" s="71"/>
-    </row>
-    <row r="11" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="100" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="100"/>
-      <c r="C11" s="75">
-        <f>VLOOKUP(A11, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>30</v>
-      </c>
-      <c r="D11" s="105"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="105"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="76"/>
-      <c r="J11" s="106" t="str">
-        <f>IF(OR(G11="",D11=""),"",IF(ISERROR(VLOOKUP(A11,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G11)=TRUE,SUBSTITUTE(G11,"&lt;","",1)*1,G11)&gt;VLOOKUP(A11,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D11)=TRUE,SUBSTITUTE(D11,"&lt;","",1)*1,D11)&gt;VLOOKUP(A11,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D11)=TRUE,SUBSTITUTE(D11,"&lt;","",1)*1,D11)-((IF(ISTEXT(D11)=TRUE,SUBSTITUTE(D11,"&lt;","",1)*1,D11)+IF(ISTEXT(G11)=TRUE,SUBSTITUTE(G11,"&lt;","",1)*1,G11))/2))/((IF(ISTEXT(D11)=TRUE,SUBSTITUTE(D11,"&lt;","",1)*1,D11)+IF(ISTEXT(G11)=TRUE,SUBSTITUTE(G11,"&lt;","",1),G11))/2),"-")))</f>
-        <v/>
-      </c>
-      <c r="K11" s="107"/>
-      <c r="L11" s="100" t="str">
-        <f>IF(OR(D11="",G11=""),"",IF(AND(F11="Oui",I11="Oui"),"Oui",IF(J11="-","Oui",IF(OR(G11&gt;VLOOKUP($D11,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D11&gt;VLOOKUP($D11,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G11&lt;=VLOOKUP($D11,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J11)&lt;=VLOOKUP($D11,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J11)&lt;=VLOOKUP($D11,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
-        <v/>
-      </c>
-      <c r="M11" s="100"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="70"/>
-      <c r="P11" s="71"/>
-    </row>
-    <row r="12" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="100" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="100"/>
-      <c r="C12" s="75">
-        <f>VLOOKUP(A12, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>10</v>
-      </c>
-      <c r="D12" s="105"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="106" t="str">
-        <f>IF(OR(G12="",D12=""),"",IF(ISERROR(VLOOKUP(A12,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G12)=TRUE,SUBSTITUTE(G12,"&lt;","",1)*1,G12)&gt;VLOOKUP(A12,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D12)=TRUE,SUBSTITUTE(D12,"&lt;","",1)*1,D12)&gt;VLOOKUP(A12,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D12)=TRUE,SUBSTITUTE(D12,"&lt;","",1)*1,D12)-((IF(ISTEXT(D12)=TRUE,SUBSTITUTE(D12,"&lt;","",1)*1,D12)+IF(ISTEXT(G12)=TRUE,SUBSTITUTE(G12,"&lt;","",1)*1,G12))/2))/((IF(ISTEXT(D12)=TRUE,SUBSTITUTE(D12,"&lt;","",1)*1,D12)+IF(ISTEXT(G12)=TRUE,SUBSTITUTE(G12,"&lt;","",1),G12))/2),"-")))</f>
-        <v/>
-      </c>
-      <c r="K12" s="107"/>
-      <c r="L12" s="100" t="str">
-        <f>IF(OR(D12="",G12=""),"",IF(AND(F12="Oui",I12="Oui"),"Oui",IF(J12="-","Oui",IF(OR(G12&gt;VLOOKUP($D12,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D12&gt;VLOOKUP($D12,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G12&lt;=VLOOKUP($D12,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J12)&lt;=VLOOKUP($D12,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J12)&lt;=VLOOKUP($D12,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
-        <v/>
-      </c>
-      <c r="M12" s="100"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="70"/>
-      <c r="P12" s="71"/>
-    </row>
-    <row r="13" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="100" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="100"/>
-      <c r="C13" s="75">
-        <f>VLOOKUP(A13, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="D13" s="105"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="106" t="str">
-        <f>IF(OR(G13="",D13=""),"",IF(ISERROR(VLOOKUP(A13,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G13)=TRUE,SUBSTITUTE(G13,"&lt;","",1)*1,G13)&gt;VLOOKUP(A13,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D13)=TRUE,SUBSTITUTE(D13,"&lt;","",1)*1,D13)&gt;VLOOKUP(A13,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D13)=TRUE,SUBSTITUTE(D13,"&lt;","",1)*1,D13)-((IF(ISTEXT(D13)=TRUE,SUBSTITUTE(D13,"&lt;","",1)*1,D13)+IF(ISTEXT(G13)=TRUE,SUBSTITUTE(G13,"&lt;","",1)*1,G13))/2))/((IF(ISTEXT(D13)=TRUE,SUBSTITUTE(D13,"&lt;","",1)*1,D13)+IF(ISTEXT(G13)=TRUE,SUBSTITUTE(G13,"&lt;","",1),G13))/2),"-")))</f>
-        <v/>
-      </c>
-      <c r="K13" s="107"/>
-      <c r="L13" s="100" t="str">
-        <f>IF(OR(D13="",G13=""),"",IF(AND(F13="Oui",I13="Oui"),"Oui",IF(J13="-","Oui",IF(OR(G13&gt;VLOOKUP($D13,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D13&gt;VLOOKUP($D13,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G13&lt;=VLOOKUP($D13,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J13)&lt;=VLOOKUP($D13,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J13)&lt;=VLOOKUP($D13,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
-        <v/>
-      </c>
-      <c r="M13" s="100"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="70"/>
-      <c r="P13" s="71"/>
-    </row>
-    <row r="14" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="100" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="100"/>
-      <c r="C14" s="75">
-        <f>VLOOKUP(A14, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>0.5</v>
-      </c>
-      <c r="D14" s="105"/>
-      <c r="E14" s="105"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="105"/>
-      <c r="H14" s="105"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="106" t="str">
-        <f>IF(OR(G14="",D14=""),"",IF(ISERROR(VLOOKUP(A14,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G14)=TRUE,SUBSTITUTE(G14,"&lt;","",1)*1,G14)&gt;VLOOKUP(A14,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D14)=TRUE,SUBSTITUTE(D14,"&lt;","",1)*1,D14)&gt;VLOOKUP(A14,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D14)=TRUE,SUBSTITUTE(D14,"&lt;","",1)*1,D14)-((IF(ISTEXT(D14)=TRUE,SUBSTITUTE(D14,"&lt;","",1)*1,D14)+IF(ISTEXT(G14)=TRUE,SUBSTITUTE(G14,"&lt;","",1)*1,G14))/2))/((IF(ISTEXT(D14)=TRUE,SUBSTITUTE(D14,"&lt;","",1)*1,D14)+IF(ISTEXT(G14)=TRUE,SUBSTITUTE(G14,"&lt;","",1),G14))/2),"-")))</f>
-        <v/>
-      </c>
-      <c r="K14" s="107"/>
-      <c r="L14" s="100" t="str">
-        <f>IF(OR(D14="",G14=""),"",IF(AND(F14="Oui",I14="Oui"),"Oui",IF(J14="-","Oui",IF(OR(G14&gt;VLOOKUP($D14,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D14&gt;VLOOKUP($D14,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G14&lt;=VLOOKUP($D14,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J14)&lt;=VLOOKUP($D14,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J14)&lt;=VLOOKUP($D14,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
-        <v/>
-      </c>
-      <c r="M14" s="100"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="71"/>
-    </row>
-    <row r="15" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="100"/>
-      <c r="C15" s="75">
-        <f>VLOOKUP(A15, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="76"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="106" t="str">
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="154"/>
+      <c r="H15" s="154"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="140" t="str">
         <f>IF(OR(G15="",D15=""),"",IF(ISERROR(VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G15)=TRUE,SUBSTITUTE(G15,"&lt;","",1)*1,G15)&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)-((IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)+IF(ISTEXT(G15)=TRUE,SUBSTITUTE(G15,"&lt;","",1)*1,G15))/2))/((IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)+IF(ISTEXT(G15)=TRUE,SUBSTITUTE(G15,"&lt;","",1),G15))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K15" s="107"/>
-      <c r="L15" s="100" t="str">
-        <f>IF(OR(D15="",G15=""),"",IF(AND(F15="Oui",I15="Oui"),"Oui",IF(J15="-","Oui",IF(OR(G15&gt;VLOOKUP($D15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D15&gt;VLOOKUP($D15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G15&lt;=VLOOKUP($D15,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J15)&lt;=VLOOKUP($D15,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J15)&lt;=VLOOKUP($D15,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+      <c r="K15" s="141"/>
+      <c r="L15" s="138" t="str">
+        <f>IF(OR(D15="",G15=""),"",IF(AND(F15="Oui",I15="Oui"),"Oui",IF(J15="-","Oui",IF(OR(G15&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D15&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G15&lt;=VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J15)&lt;=VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J15)&lt;=VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M15" s="100"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="71"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="80" t="str">
+        <f>IF(OR(AND(ISNUMBER(D15),D15&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G15),G15&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D15,G15)&lt;=VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O15" s="76"/>
+      <c r="P15" s="68"/>
     </row>
     <row r="16" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="100" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="100"/>
-      <c r="C16" s="75">
+      <c r="A16" s="152" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="152"/>
+      <c r="C16" s="71">
         <f>VLOOKUP(A16, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>0.5</v>
-      </c>
-      <c r="D16" s="105"/>
-      <c r="E16" s="105"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="105"/>
-      <c r="H16" s="105"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="106" t="str">
+        <v>30</v>
+      </c>
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="136" t="str">
         <f>IF(OR(G16="",D16=""),"",IF(ISERROR(VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G16)=TRUE,SUBSTITUTE(G16,"&lt;","",1)*1,G16)&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)-((IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)+IF(ISTEXT(G16)=TRUE,SUBSTITUTE(G16,"&lt;","",1)*1,G16))/2))/((IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)+IF(ISTEXT(G16)=TRUE,SUBSTITUTE(G16,"&lt;","",1),G16))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K16" s="107"/>
-      <c r="L16" s="100" t="str">
-        <f>IF(OR(D16="",G16=""),"",IF(AND(F16="Oui",I16="Oui"),"Oui",IF(J16="-","Oui",IF(OR(G16&gt;VLOOKUP($D16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D16&gt;VLOOKUP($D16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G16&lt;=VLOOKUP($D16,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J16)&lt;=VLOOKUP($D16,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J16)&lt;=VLOOKUP($D16,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+      <c r="K16" s="137"/>
+      <c r="L16" s="138" t="str">
+        <f>IF(OR(D16="",G16=""),"",IF(AND(F16="Oui",I16="Oui"),"Oui",IF(J16="-","Oui",IF(OR(G16&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D16&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G16&lt;=VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J16)&lt;=VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J16)&lt;=VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M16" s="100"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="71"/>
+      <c r="M16" s="139"/>
+      <c r="N16" s="81" t="str">
+        <f>IF(OR(AND(ISNUMBER(D16),D16&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G16),G16&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D16,G16)&lt;=VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O16" s="76"/>
+      <c r="P16" s="68"/>
     </row>
     <row r="17" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="100" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="100"/>
-      <c r="C17" s="75">
+      <c r="A17" s="152" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="152"/>
+      <c r="C17" s="71">
         <f>VLOOKUP(A17, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>0.05</v>
-      </c>
-      <c r="D17" s="105"/>
-      <c r="E17" s="105"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="106" t="str">
+        <v>10</v>
+      </c>
+      <c r="D17" s="135"/>
+      <c r="E17" s="135"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="136" t="str">
         <f>IF(OR(G17="",D17=""),"",IF(ISERROR(VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G17)=TRUE,SUBSTITUTE(G17,"&lt;","",1)*1,G17)&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)-((IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)+IF(ISTEXT(G17)=TRUE,SUBSTITUTE(G17,"&lt;","",1)*1,G17))/2))/((IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)+IF(ISTEXT(G17)=TRUE,SUBSTITUTE(G17,"&lt;","",1),G17))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K17" s="107"/>
-      <c r="L17" s="100" t="str">
-        <f>IF(OR(D17="",G17=""),"",IF(AND(F17="Oui",I17="Oui"),"Oui",IF(J17="-","Oui",IF(OR(G17&gt;VLOOKUP($D17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D17&gt;VLOOKUP($D17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G17&lt;=VLOOKUP($D17,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J17)&lt;=VLOOKUP($D17,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J17)&lt;=VLOOKUP($D17,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+      <c r="K17" s="137"/>
+      <c r="L17" s="138" t="str">
+        <f>IF(OR(D17="",G17=""),"",IF(AND(F17="Oui",I17="Oui"),"Oui",IF(J17="-","Oui",IF(OR(G17&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D17&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G17&lt;=VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J17)&lt;=VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J17)&lt;=VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M17" s="100"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="71"/>
+      <c r="M17" s="139"/>
+      <c r="N17" s="81" t="str">
+        <f>IF(OR(AND(ISNUMBER(D17),D17&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G17),G17&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D17,G17)&lt;=VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O17" s="76"/>
+      <c r="P17" s="68"/>
     </row>
     <row r="18" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="100" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="100"/>
-      <c r="C18" s="75">
+      <c r="A18" s="152" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="152"/>
+      <c r="C18" s="71">
         <f>VLOOKUP(A18, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="D18" s="105"/>
-      <c r="E18" s="105"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="106" t="str">
+        <v>2</v>
+      </c>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="74"/>
+      <c r="J18" s="136" t="str">
         <f>IF(OR(G18="",D18=""),"",IF(ISERROR(VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G18)=TRUE,SUBSTITUTE(G18,"&lt;","",1)*1,G18)&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)-((IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)+IF(ISTEXT(G18)=TRUE,SUBSTITUTE(G18,"&lt;","",1)*1,G18))/2))/((IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)+IF(ISTEXT(G18)=TRUE,SUBSTITUTE(G18,"&lt;","",1),G18))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K18" s="107"/>
-      <c r="L18" s="100" t="str">
-        <f>IF(OR(D18="",G18=""),"",IF(AND(F18="Oui",I18="Oui"),"Oui",IF(J18="-","Oui",IF(OR(G18&gt;VLOOKUP($D18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D18&gt;VLOOKUP($D18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G18&lt;=VLOOKUP($D18,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J18)&lt;=VLOOKUP($D18,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J18)&lt;=VLOOKUP($D18,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+      <c r="K18" s="137"/>
+      <c r="L18" s="138" t="str">
+        <f>IF(OR(D18="",G18=""),"",IF(AND(F18="Oui",I18="Oui"),"Oui",IF(J18="-","Oui",IF(OR(G18&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D18&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G18&lt;=VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J18)&lt;=VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J18)&lt;=VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M18" s="100"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="70"/>
-      <c r="P18" s="71"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="81" t="str">
+        <f>IF(OR(AND(ISNUMBER(D18),D18&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G18),G18&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D18,G18)&lt;=VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O18" s="76"/>
+      <c r="P18" s="68"/>
     </row>
     <row r="19" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="100" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="100"/>
-      <c r="C19" s="75">
+      <c r="A19" s="152" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="152"/>
+      <c r="C19" s="71">
         <f>VLOOKUP(A19, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>0.05</v>
-      </c>
-      <c r="D19" s="105"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="105"/>
-      <c r="H19" s="105"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="106" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="135"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="136" t="str">
         <f>IF(OR(G19="",D19=""),"",IF(ISERROR(VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G19)=TRUE,SUBSTITUTE(G19,"&lt;","",1)*1,G19)&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)-((IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)+IF(ISTEXT(G19)=TRUE,SUBSTITUTE(G19,"&lt;","",1)*1,G19))/2))/((IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)+IF(ISTEXT(G19)=TRUE,SUBSTITUTE(G19,"&lt;","",1),G19))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K19" s="107"/>
-      <c r="L19" s="100" t="str">
-        <f>IF(OR(D19="",G19=""),"",IF(AND(F19="Oui",I19="Oui"),"Oui",IF(J19="-","Oui",IF(OR(G19&gt;VLOOKUP($D19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D19&gt;VLOOKUP($D19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G19&lt;=VLOOKUP($D19,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J19)&lt;=VLOOKUP($D19,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J19)&lt;=VLOOKUP($D19,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+      <c r="K19" s="137"/>
+      <c r="L19" s="138" t="str">
+        <f>IF(OR(D19="",G19=""),"",IF(AND(F19="Oui",I19="Oui"),"Oui",IF(J19="-","Oui",IF(OR(G19&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D19&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G19&lt;=VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J19)&lt;=VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J19)&lt;=VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M19" s="100"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="70"/>
-      <c r="P19" s="71"/>
+      <c r="M19" s="139"/>
+      <c r="N19" s="81" t="str">
+        <f>IF(OR(AND(ISNUMBER(D19),D19&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G19),G19&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D19,G19)&lt;=VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O19" s="76"/>
+      <c r="P19" s="68"/>
     </row>
     <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="100" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" s="100"/>
-      <c r="C20" s="75">
+      <c r="A20" s="152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="152"/>
+      <c r="C20" s="71">
         <f>VLOOKUP(A20, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="76"/>
-      <c r="J20" s="106" t="str">
+        <v>1</v>
+      </c>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="74"/>
+      <c r="J20" s="136" t="str">
         <f>IF(OR(G20="",D20=""),"",IF(ISERROR(VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G20)=TRUE,SUBSTITUTE(G20,"&lt;","",1)*1,G20)&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)-((IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)+IF(ISTEXT(G20)=TRUE,SUBSTITUTE(G20,"&lt;","",1)*1,G20))/2))/((IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)+IF(ISTEXT(G20)=TRUE,SUBSTITUTE(G20,"&lt;","",1),G20))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K20" s="107"/>
-      <c r="L20" s="100" t="str">
-        <f>IF(OR(D20="",G20=""),"",IF(AND(F20="Oui",I20="Oui"),"Oui",IF(J20="-","Oui",IF(OR(G20&gt;VLOOKUP($D20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D20&gt;VLOOKUP($D20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G20&lt;=VLOOKUP($D20,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J20)&lt;=VLOOKUP($D20,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J20)&lt;=VLOOKUP($D20,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+      <c r="K20" s="137"/>
+      <c r="L20" s="138" t="str">
+        <f>IF(OR(D20="",G20=""),"",IF(AND(F20="Oui",I20="Oui"),"Oui",IF(J20="-","Oui",IF(OR(G20&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D20&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G20&lt;=VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J20)&lt;=VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J20)&lt;=VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M20" s="100"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="70"/>
-      <c r="P20" s="71"/>
+      <c r="M20" s="139"/>
+      <c r="N20" s="81" t="str">
+        <f>IF(OR(AND(ISNUMBER(D20),D20&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G20),G20&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D20,G20)&lt;=VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O20" s="76"/>
+      <c r="P20" s="68"/>
     </row>
     <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="121" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="121"/>
-      <c r="C21" s="69">
+      <c r="A21" s="152" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="152"/>
+      <c r="C21" s="71">
         <f>VLOOKUP(A21, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="122"/>
-      <c r="H21" s="122"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="123" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="135"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="135"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="136" t="str">
         <f>IF(OR(G21="",D21=""),"",IF(ISERROR(VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G21)=TRUE,SUBSTITUTE(G21,"&lt;","",1)*1,G21)&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)-((IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)+IF(ISTEXT(G21)=TRUE,SUBSTITUTE(G21,"&lt;","",1)*1,G21))/2))/((IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)+IF(ISTEXT(G21)=TRUE,SUBSTITUTE(G21,"&lt;","",1),G21))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K21" s="124"/>
-      <c r="L21" s="121" t="str">
-        <f>IF(OR(D21="",G21=""),"",IF(AND(F21="Oui",I21="Oui"),"Oui",IF(J21="-","Oui",IF(OR(G21&gt;VLOOKUP($D21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D21&gt;VLOOKUP($D21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G21&lt;=VLOOKUP($D21,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J21)&lt;=VLOOKUP($D21,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J21)&lt;=VLOOKUP($D21,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+      <c r="K21" s="137"/>
+      <c r="L21" s="138" t="str">
+        <f>IF(OR(D21="",G21=""),"",IF(AND(F21="Oui",I21="Oui"),"Oui",IF(J21="-","Oui",IF(OR(G21&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D21&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G21&lt;=VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J21)&lt;=VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J21)&lt;=VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M21" s="121"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="70"/>
-      <c r="P21" s="71"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="81" t="str">
+        <f>IF(OR(AND(ISNUMBER(D21),D21&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G21),G21&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D21,G21)&lt;=VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O21" s="76"/>
+      <c r="P21" s="68"/>
     </row>
     <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="104" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="104"/>
-      <c r="C22" s="73">
+      <c r="A22" s="152" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="152"/>
+      <c r="C22" s="71">
         <f>VLOOKUP(A22, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="118"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="119" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="D22" s="135"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="135"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="136" t="str">
         <f>IF(OR(G22="",D22=""),"",IF(ISERROR(VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G22)=TRUE,SUBSTITUTE(G22,"&lt;","",1)*1,G22)&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)-((IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)+IF(ISTEXT(G22)=TRUE,SUBSTITUTE(G22,"&lt;","",1)*1,G22))/2))/((IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)+IF(ISTEXT(G22)=TRUE,SUBSTITUTE(G22,"&lt;","",1),G22))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K22" s="120"/>
-      <c r="L22" s="104" t="str">
-        <f>IF(OR(D22="",G22=""),"",IF(AND(F22="Oui",I22="Oui"),"Oui",IF(J22="-","Oui",IF(OR(G22&gt;VLOOKUP($D22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D22&gt;VLOOKUP($D22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G22&lt;=VLOOKUP($D22,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J22)&lt;=VLOOKUP($D22,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J22)&lt;=VLOOKUP($D22,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+      <c r="K22" s="137"/>
+      <c r="L22" s="138" t="str">
+        <f>IF(OR(D22="",G22=""),"",IF(AND(F22="Oui",I22="Oui"),"Oui",IF(J22="-","Oui",IF(OR(G22&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D22&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G22&lt;=VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J22)&lt;=VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J22)&lt;=VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M22" s="104"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="71"/>
+      <c r="M22" s="139"/>
+      <c r="N22" s="81" t="str">
+        <f>IF(OR(AND(ISNUMBER(D22),D22&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G22),G22&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D22,G22)&lt;=VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O22" s="76"/>
+      <c r="P22" s="68"/>
     </row>
     <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="70"/>
-      <c r="P23" s="71"/>
+      <c r="A23" s="152" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="152"/>
+      <c r="C23" s="71">
+        <f>VLOOKUP(A23, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D23" s="135"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="135"/>
+      <c r="I23" s="74"/>
+      <c r="J23" s="136" t="str">
+        <f>IF(OR(G23="",D23=""),"",IF(ISERROR(VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G23)=TRUE,SUBSTITUTE(G23,"&lt;","",1)*1,G23)&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)-((IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)+IF(ISTEXT(G23)=TRUE,SUBSTITUTE(G23,"&lt;","",1)*1,G23))/2))/((IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)+IF(ISTEXT(G23)=TRUE,SUBSTITUTE(G23,"&lt;","",1),G23))/2),"-")))</f>
+        <v/>
+      </c>
+      <c r="K23" s="137"/>
+      <c r="L23" s="138" t="str">
+        <f>IF(OR(D23="",G23=""),"",IF(AND(F23="Oui",I23="Oui"),"Oui",IF(J23="-","Oui",IF(OR(G23&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D23&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G23&lt;=VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J23)&lt;=VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J23)&lt;=VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+        <v/>
+      </c>
+      <c r="M23" s="139"/>
+      <c r="N23" s="81" t="str">
+        <f>IF(OR(AND(ISNUMBER(D23),D23&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G23),G23&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D23,G23)&lt;=VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O23" s="76"/>
+      <c r="P23" s="68"/>
     </row>
     <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="108" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" s="108"/>
-      <c r="C24" s="108"/>
-      <c r="D24" s="108"/>
-      <c r="E24" s="108"/>
-      <c r="F24" s="108"/>
-      <c r="G24" s="108"/>
-      <c r="H24" s="108"/>
-      <c r="I24" s="108"/>
-      <c r="J24" s="108"/>
-      <c r="K24" s="108"/>
-      <c r="L24" s="108"/>
-      <c r="M24" s="108"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="70"/>
-      <c r="P24" s="71"/>
+      <c r="A24" s="152" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="152"/>
+      <c r="C24" s="71">
+        <f>VLOOKUP(A24, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
+        <v>0.05</v>
+      </c>
+      <c r="D24" s="135"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="135"/>
+      <c r="I24" s="74"/>
+      <c r="J24" s="136" t="str">
+        <f>IF(OR(G24="",D24=""),"",IF(ISERROR(VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G24)=TRUE,SUBSTITUTE(G24,"&lt;","",1)*1,G24)&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)-((IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)+IF(ISTEXT(G24)=TRUE,SUBSTITUTE(G24,"&lt;","",1)*1,G24))/2))/((IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)+IF(ISTEXT(G24)=TRUE,SUBSTITUTE(G24,"&lt;","",1),G24))/2),"-")))</f>
+        <v/>
+      </c>
+      <c r="K24" s="137"/>
+      <c r="L24" s="138" t="str">
+        <f>IF(OR(D24="",G24=""),"",IF(AND(F24="Oui",I24="Oui"),"Oui",IF(J24="-","Oui",IF(OR(G24&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D24&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G24&lt;=VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J24)&lt;=VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J24)&lt;=VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+        <v/>
+      </c>
+      <c r="M24" s="139"/>
+      <c r="N24" s="81" t="str">
+        <f>IF(OR(AND(ISNUMBER(D24),D24&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G24),G24&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D24,G24)&lt;=VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O24" s="76"/>
+      <c r="P24" s="68"/>
     </row>
     <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="109"/>
-      <c r="B25" s="110"/>
-      <c r="C25" s="110"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="110"/>
-      <c r="L25" s="110"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="70"/>
-      <c r="P25" s="71"/>
+      <c r="A25" s="152" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="152"/>
+      <c r="C25" s="71">
+        <f>VLOOKUP(A25, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="155"/>
+      <c r="E25" s="155"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="155"/>
+      <c r="H25" s="155"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="156" t="str">
+        <f>IF(OR(G25="",D25=""),"",IF(ISERROR(VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G25)=TRUE,SUBSTITUTE(G25,"&lt;","",1)*1,G25)&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)-((IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)+IF(ISTEXT(G25)=TRUE,SUBSTITUTE(G25,"&lt;","",1)*1,G25))/2))/((IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)+IF(ISTEXT(G25)=TRUE,SUBSTITUTE(G25,"&lt;","",1),G25))/2),"-")))</f>
+        <v/>
+      </c>
+      <c r="K25" s="157"/>
+      <c r="L25" s="158" t="str">
+        <f>IF(OR(D25="",G25=""),"",IF(AND(F25="Oui",I25="Oui"),"Oui",IF(J25="-","Oui",IF(OR(G25&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D25&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G25&lt;=VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J25)&lt;=VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J25)&lt;=VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+        <v/>
+      </c>
+      <c r="M25" s="159"/>
+      <c r="N25" s="81" t="str">
+        <f>IF(OR(AND(ISNUMBER(D25),D25&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G25),G25&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D25,G25)&lt;=VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O25" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="P25" s="68"/>
     </row>
     <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="112"/>
-      <c r="B26" s="113"/>
-      <c r="C26" s="113"/>
-      <c r="D26" s="113"/>
-      <c r="E26" s="113"/>
-      <c r="F26" s="113"/>
-      <c r="G26" s="113"/>
-      <c r="H26" s="113"/>
-      <c r="I26" s="113"/>
-      <c r="J26" s="113"/>
-      <c r="K26" s="113"/>
-      <c r="L26" s="113"/>
-      <c r="M26" s="113"/>
-      <c r="N26" s="114"/>
-      <c r="O26" s="70"/>
-      <c r="P26" s="71"/>
+      <c r="A26" s="167" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="167"/>
+      <c r="C26" s="67">
+        <f>VLOOKUP(A26, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="D26" s="168"/>
+      <c r="E26" s="168"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="168"/>
+      <c r="H26" s="168"/>
+      <c r="I26" s="88"/>
+      <c r="J26" s="156" t="str">
+        <f>IF(OR(G26="",D26=""),"",IF(ISERROR(VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G26)=TRUE,SUBSTITUTE(G26,"&lt;","",1)*1,G26)&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)-((IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)+IF(ISTEXT(G26)=TRUE,SUBSTITUTE(G26,"&lt;","",1)*1,G26))/2))/((IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)+IF(ISTEXT(G26)=TRUE,SUBSTITUTE(G26,"&lt;","",1),G26))/2),"-")))</f>
+        <v/>
+      </c>
+      <c r="K26" s="157"/>
+      <c r="L26" s="169" t="str">
+        <f>IF(OR(D26="",G26=""),"",IF(AND(F26="Oui",I26="Oui"),"Oui",IF(J26="-","Oui",IF(OR(G26&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D26&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G26&lt;=VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J26)&lt;=VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J26)&lt;=VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+        <v/>
+      </c>
+      <c r="M26" s="170"/>
+      <c r="N26" s="82" t="str">
+        <f>IF(OR(AND(ISNUMBER(D26),D26&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G26),G26&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D26,G26)&lt;=VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O26" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="P26" s="68"/>
     </row>
     <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="115"/>
-      <c r="B27" s="116"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116"/>
-      <c r="L27" s="116"/>
-      <c r="M27" s="116"/>
-      <c r="N27" s="117"/>
-      <c r="O27" s="70"/>
-      <c r="P27" s="71"/>
+      <c r="A27" s="160" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="160"/>
+      <c r="C27" s="70">
+        <f>VLOOKUP(A27, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="161"/>
+      <c r="E27" s="161"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="161"/>
+      <c r="H27" s="161"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="162" t="str">
+        <f>IF(OR(G27="",D27=""),"",IF(ISERROR(VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G27)=TRUE,SUBSTITUTE(G27,"&lt;","",1)*1,G27)&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)-((IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)+IF(ISTEXT(G27)=TRUE,SUBSTITUTE(G27,"&lt;","",1)*1,G27))/2))/((IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)+IF(ISTEXT(G27)=TRUE,SUBSTITUTE(G27,"&lt;","",1),G27))/2),"-")))</f>
+        <v/>
+      </c>
+      <c r="K27" s="163"/>
+      <c r="L27" s="164" t="str">
+        <f>IF(OR(D27="",G27=""),"",IF(AND(F27="Oui",I27="Oui"),"Oui",IF(J27="-","Oui",IF(OR(G27&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D27&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G27&lt;=VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J27)&lt;=VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J27)&lt;=VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
+        <v/>
+      </c>
+      <c r="M27" s="165"/>
+      <c r="N27" s="83" t="str">
+        <f>IF(OR(AND(ISNUMBER(D27),D27&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G27),G27&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D27,G27)&lt;=VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
+        <v/>
+      </c>
+      <c r="O27" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="P27" s="68"/>
     </row>
     <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="72"/>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="70"/>
-      <c r="P28" s="71"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="77"/>
+      <c r="O28" s="76"/>
+      <c r="P28" s="68"/>
+    </row>
+    <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="166" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="166"/>
+      <c r="C29" s="166"/>
+      <c r="D29" s="166"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="166"/>
+      <c r="G29" s="166"/>
+      <c r="H29" s="166"/>
+      <c r="I29" s="166"/>
+      <c r="J29" s="166"/>
+      <c r="K29" s="166"/>
+      <c r="L29" s="166"/>
+      <c r="M29" s="166"/>
+      <c r="N29" s="77"/>
+      <c r="O29" s="76"/>
+      <c r="P29" s="68"/>
+    </row>
+    <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="113"/>
+      <c r="B30" s="114"/>
+      <c r="C30" s="114"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="114"/>
+      <c r="I30" s="114"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="114"/>
+      <c r="L30" s="114"/>
+      <c r="M30" s="114"/>
+      <c r="N30" s="115"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="68"/>
+    </row>
+    <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="116"/>
+      <c r="B31" s="117"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="117"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="117"/>
+      <c r="M31" s="117"/>
+      <c r="N31" s="118"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="68"/>
+    </row>
+    <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="116"/>
+      <c r="B32" s="117"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="117"/>
+      <c r="I32" s="117"/>
+      <c r="J32" s="117"/>
+      <c r="K32" s="117"/>
+      <c r="L32" s="117"/>
+      <c r="M32" s="117"/>
+      <c r="N32" s="118"/>
+      <c r="O32" s="76"/>
+      <c r="P32" s="68"/>
+    </row>
+    <row r="33" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="116"/>
+      <c r="B33" s="117"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="117"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="117"/>
+      <c r="G33" s="117"/>
+      <c r="H33" s="117"/>
+      <c r="I33" s="117"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="117"/>
+      <c r="L33" s="117"/>
+      <c r="M33" s="117"/>
+      <c r="N33" s="118"/>
+      <c r="O33" s="76"/>
+      <c r="P33" s="68"/>
+    </row>
+    <row r="34" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="119"/>
+      <c r="B34" s="120"/>
+      <c r="C34" s="120"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="120"/>
+      <c r="H34" s="120"/>
+      <c r="I34" s="120"/>
+      <c r="J34" s="120"/>
+      <c r="K34" s="120"/>
+      <c r="L34" s="120"/>
+      <c r="M34" s="120"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="76"/>
+      <c r="P34" s="68"/>
+    </row>
+    <row r="35" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="69"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="69"/>
+      <c r="L35" s="69"/>
+      <c r="M35" s="69"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="76"/>
+      <c r="P35" s="68"/>
     </row>
   </sheetData>
-  <mergeCells count="91">
-    <mergeCell ref="A21:B21"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="E0vgYSLd6IzN3zQpTtpwF407YWeiFI/59Uy/KfslbgamR5SvUT6ebXKuaEoF2kOs5D1P4aRMpT40oh0DZU5zTQ==" saltValue="ZofzeV6n80OCTfHoPp6DgQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <mergeCells count="98">
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="J21:K21"/>
     <mergeCell ref="L21:M21"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G24:H24"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A25:N27"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K3:N3"/>
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="J18:K18"/>
     <mergeCell ref="L18:M18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="L17:M17"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:E9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="D3:G4"/>
     <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A30:N34"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="A12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="G12:H14"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="H7:N7"/>
   </mergeCells>
-  <conditionalFormatting sqref="H3:J3">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>$D3="Oui"</formula>
+  <conditionalFormatting sqref="A9:N9">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>$J$26 = "Oui"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:J4">
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>$D3="Oui"</formula>
+  <conditionalFormatting sqref="G8:G9">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>"Oui"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+      <formula>"Non"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:N3">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>$D3="Oui"</formula>
+  <conditionalFormatting sqref="H3:J3">
+    <cfRule type="expression" dxfId="5" priority="59">
+      <formula>$A3="Oui"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:N4">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$D3="Oui"</formula>
+  <conditionalFormatting sqref="J15:K26">
+    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
+      <formula>IF(ABS(J15)&gt;N15,TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I10:I22 F10:F22" xr:uid="{6B1CE0E0-F0EA-479B-91B1-FBE1DCD7BCA9}">
+  <conditionalFormatting sqref="J15:K27">
+    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
+      <formula>IF(ABS(J15)&lt;=N15,TRUE,FALSE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="expression" dxfId="2" priority="62">
+      <formula>$A3="Non"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L15:L27">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+      <formula>"Oui"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+      <formula>"Non"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 L15:M27 G8:G9" xr:uid="{D9571EBC-6FF8-4CB6-B6B8-5654E9E0B57B}">
+      <formula1>LISTE_1</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{6478A3AA-E53F-46B7-8EB5-18387D457970}">
+      <formula1>listePreleveurs</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I15:I27 F15:F27" xr:uid="{9827A3EB-1CBF-4ADD-9F4D-3F87BB2F1115}">
       <formula1>"Oui,Non"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L10:M22" xr:uid="{C5B839F4-B232-41AD-9911-11EABC14136A}">
-      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x12ac">
-          <x12ac:list>"""Oui""""","""Non""",""""""</x12ac:list>
-        </mc:Choice>
-        <mc:Fallback>
-          <formula1>"""Oui"""",""Non"","""""</formula1>
-        </mc:Fallback>
-      </mc:AlternateContent>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Coefficient Analytique" prompt="Le coefficient est égale au nombre d'analyse conforme / nombre d'analyse réalisées x le score de pénalité" sqref="N12" xr:uid="{98B0E8A5-51FC-414B-9825-B4FB9B54760B}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3178,340 +3656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <sheetPr codeName="Feuil7"/>
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="12.75" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="2.703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5859375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="7" customWidth="1"/>
-    <col min="6" max="6" width="2.703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1171875" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="11" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.41015625" style="1" hidden="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="13" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="10"/>
-    </row>
-    <row r="2" spans="1:6" ht="15.7" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="10"/>
-      <c r="B2" s="125" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="13"/>
-    </row>
-    <row r="3" spans="1:6" ht="13" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" ht="51" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="14"/>
-    </row>
-    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="10"/>
-      <c r="B5" s="18">
-        <v>1458</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="21">
-        <v>100</v>
-      </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="10"/>
-      <c r="B6" s="22">
-        <v>1114</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="25">
-        <v>10</v>
-      </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="10"/>
-      <c r="B7" s="22">
-        <v>1115</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="25">
-        <v>100</v>
-      </c>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="10"/>
-      <c r="B8" s="22">
-        <v>1116</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="25">
-        <v>100</v>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="10"/>
-      <c r="B9" s="22">
-        <v>1117</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="25">
-        <v>100</v>
-      </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="10"/>
-      <c r="B10" s="22">
-        <v>1118</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="25">
-        <v>1000</v>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="10"/>
-      <c r="B11" s="22">
-        <v>6616</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="25">
-        <v>10</v>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="10"/>
-      <c r="B12" s="22">
-        <v>1497</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="25">
-        <v>10</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="10"/>
-      <c r="B13" s="22">
-        <v>1191</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="25">
-        <v>100</v>
-      </c>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="10"/>
-      <c r="B14" s="26">
-        <v>1204</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="25">
-        <v>1000</v>
-      </c>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="10"/>
-      <c r="B15" s="26">
-        <v>1517</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="25">
-        <v>10</v>
-      </c>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="10"/>
-      <c r="B16" s="26">
-        <v>6598</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="25">
-        <v>50</v>
-      </c>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" spans="1:6" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="28"/>
-      <c r="B17" s="26">
-        <v>6600</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="25">
-        <v>100</v>
-      </c>
-      <c r="F17" s="28"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="10"/>
-      <c r="B18" s="26">
-        <v>1278</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="25">
-        <v>10</v>
-      </c>
-      <c r="F18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="10"/>
-      <c r="B19" s="26">
-        <v>2879</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="25">
-        <v>1000</v>
-      </c>
-      <c r="F19" s="10"/>
-    </row>
-    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="10"/>
-      <c r="B20" s="29">
-        <v>1780</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="32">
-        <v>10</v>
-      </c>
-      <c r="F20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <sheetPr codeName="Feuil3"/>
   <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="12.75" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
@@ -3532,855 +3677,854 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="10"/>
-      <c r="B1" s="10"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
+      <c r="A1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
     </row>
     <row r="2" spans="1:11" ht="15.7" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="10"/>
-      <c r="B2" s="125" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="10"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="172"/>
+      <c r="J2" s="173"/>
+      <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="13" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" ht="51" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" s="2" customFormat="1" ht="67.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="39" t="s">
+      <c r="J4" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="40"/>
+      <c r="K4" s="39"/>
     </row>
     <row r="5" spans="1:11" ht="14.7" x14ac:dyDescent="0.4">
-      <c r="A5" s="10"/>
-      <c r="B5" s="41">
+      <c r="A5" s="9"/>
+      <c r="B5" s="40">
         <v>1313</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="42">
         <v>3</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="41">
         <v>15</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="43">
         <v>80</v>
       </c>
-      <c r="H5" s="45">
+      <c r="H5" s="44">
         <v>0.3</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="45">
         <v>80</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="46">
         <v>0.2</v>
       </c>
-      <c r="K5" s="10"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:11" ht="14.7" x14ac:dyDescent="0.4">
-      <c r="A6" s="10"/>
-      <c r="B6" s="48">
+      <c r="A6" s="9"/>
+      <c r="B6" s="47">
         <v>1314</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="49">
         <v>30</v>
       </c>
-      <c r="F6" s="49">
+      <c r="F6" s="48">
         <v>80</v>
       </c>
-      <c r="G6" s="51">
+      <c r="G6" s="50">
         <v>250</v>
       </c>
-      <c r="H6" s="52">
+      <c r="H6" s="51">
         <v>0.2</v>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="50">
         <v>250</v>
       </c>
-      <c r="J6" s="52">
+      <c r="J6" s="51">
         <v>0.1</v>
       </c>
-      <c r="K6" s="10"/>
+      <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:11" ht="14.7" x14ac:dyDescent="0.4">
-      <c r="A7" s="10"/>
-      <c r="B7" s="48">
+      <c r="A7" s="9"/>
+      <c r="B7" s="47">
         <v>6396</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="49">
         <v>10</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="48">
         <v>20</v>
       </c>
-      <c r="G7" s="51">
+      <c r="G7" s="50">
         <v>150</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="51">
         <v>0.2</v>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="50">
         <v>150</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7" s="51">
         <v>0.1</v>
       </c>
-      <c r="K7" s="10"/>
+      <c r="K7" s="9"/>
     </row>
     <row r="8" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A8" s="10"/>
-      <c r="B8" s="48">
+      <c r="A8" s="9"/>
+      <c r="B8" s="47">
         <v>1305</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="49" t="s">
+      <c r="D8" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="50">
+      <c r="E8" s="49">
         <v>2</v>
       </c>
-      <c r="F8" s="49">
+      <c r="F8" s="48">
         <v>15</v>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="50">
         <v>60</v>
       </c>
-      <c r="H8" s="52">
+      <c r="H8" s="51">
         <v>0.3</v>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="50">
         <v>60</v>
       </c>
-      <c r="J8" s="52">
+      <c r="J8" s="51">
         <v>0.2</v>
       </c>
-      <c r="K8" s="10"/>
+      <c r="K8" s="9"/>
     </row>
     <row r="9" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A9" s="10"/>
-      <c r="B9" s="53">
+      <c r="A9" s="9"/>
+      <c r="B9" s="52">
         <v>1319</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="49" t="s">
+      <c r="D9" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="50">
+      <c r="E9" s="49">
         <v>0.5</v>
       </c>
-      <c r="F9" s="49">
+      <c r="F9" s="48">
         <v>6</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="51">
+      <c r="I9" s="50">
         <v>6</v>
       </c>
-      <c r="J9" s="52">
+      <c r="J9" s="51">
         <v>0.1</v>
       </c>
-      <c r="K9" s="10"/>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A10" s="10"/>
-      <c r="B10" s="48">
+      <c r="A10" s="9"/>
+      <c r="B10" s="47">
         <v>1551</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="49">
         <v>1</v>
       </c>
-      <c r="F10" s="49">
+      <c r="F10" s="48">
         <v>6</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="4"/>
-      <c r="I10" s="51">
+      <c r="I10" s="50">
         <v>6</v>
       </c>
-      <c r="J10" s="52">
+      <c r="J10" s="51">
         <v>0.2</v>
       </c>
-      <c r="K10" s="10"/>
+      <c r="K10" s="9"/>
     </row>
     <row r="11" spans="1:11" ht="14.7" x14ac:dyDescent="0.4">
-      <c r="A11" s="10"/>
-      <c r="B11" s="53">
+      <c r="A11" s="9"/>
+      <c r="B11" s="52">
         <v>1335</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="49" t="s">
+      <c r="D11" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="49">
         <v>0.5</v>
       </c>
-      <c r="F11" s="49">
+      <c r="F11" s="48">
         <v>6</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="4"/>
-      <c r="I11" s="51">
+      <c r="I11" s="50">
         <v>6</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11" s="51">
         <v>0.1</v>
       </c>
-      <c r="K11" s="10"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" spans="1:11" ht="14.7" x14ac:dyDescent="0.4">
-      <c r="A12" s="10"/>
-      <c r="B12" s="53">
+      <c r="A12" s="9"/>
+      <c r="B12" s="52">
         <v>1339</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="49">
         <v>0.05</v>
       </c>
-      <c r="F12" s="49">
+      <c r="F12" s="48">
         <v>1</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="51">
+      <c r="I12" s="50">
         <v>1</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12" s="51">
         <v>0.2</v>
       </c>
-      <c r="K12" s="10"/>
+      <c r="K12" s="9"/>
     </row>
     <row r="13" spans="1:11" ht="14.7" x14ac:dyDescent="0.4">
-      <c r="A13" s="10"/>
-      <c r="B13" s="53">
+      <c r="A13" s="9"/>
+      <c r="B13" s="52">
         <v>1340</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="49" t="s">
+      <c r="D13" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="49">
         <v>1</v>
       </c>
-      <c r="F13" s="49">
+      <c r="F13" s="48">
         <v>5</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="4"/>
-      <c r="I13" s="51">
+      <c r="I13" s="50">
         <v>5</v>
       </c>
-      <c r="J13" s="52">
+      <c r="J13" s="51">
         <v>0.2</v>
       </c>
-      <c r="K13" s="10"/>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A14" s="10"/>
-      <c r="B14" s="48">
+      <c r="A14" s="9"/>
+      <c r="B14" s="47">
         <v>1350</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="49">
         <v>0.05</v>
       </c>
-      <c r="F14" s="49">
+      <c r="F14" s="48">
         <v>1</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="4"/>
-      <c r="I14" s="51">
+      <c r="I14" s="50">
         <v>1</v>
       </c>
-      <c r="J14" s="52">
+      <c r="J14" s="51">
         <v>0.2</v>
       </c>
-      <c r="K14" s="10"/>
+      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A15" s="10"/>
-      <c r="B15" s="48">
+      <c r="A15" s="9"/>
+      <c r="B15" s="47">
         <v>1369</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="D15" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="49">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="48">
         <v>0.5</v>
       </c>
-      <c r="G15" s="51">
+      <c r="G15" s="50">
         <v>1</v>
       </c>
-      <c r="H15" s="52">
+      <c r="H15" s="51">
         <v>0.6</v>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="50">
         <v>1</v>
       </c>
-      <c r="J15" s="52">
+      <c r="J15" s="51">
         <v>0.3</v>
       </c>
-      <c r="K15" s="10"/>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A16" s="10"/>
-      <c r="B16" s="48">
+      <c r="A16" s="9"/>
+      <c r="B16" s="47">
         <v>1388</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="54" t="s">
+      <c r="D16" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="49">
         <v>1E-3</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="48">
         <v>0.5</v>
       </c>
-      <c r="G16" s="51">
+      <c r="G16" s="50">
         <v>1</v>
       </c>
-      <c r="H16" s="52">
+      <c r="H16" s="51">
         <v>0.6</v>
       </c>
-      <c r="I16" s="51">
+      <c r="I16" s="50">
         <v>1</v>
       </c>
-      <c r="J16" s="52">
+      <c r="J16" s="51">
         <v>0.3</v>
       </c>
-      <c r="K16" s="10"/>
+      <c r="K16" s="9"/>
     </row>
     <row r="17" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A17" s="10"/>
-      <c r="B17" s="48">
+      <c r="A17" s="9"/>
+      <c r="B17" s="47">
         <v>1389</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="49">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F17" s="49">
+      <c r="F17" s="48">
         <v>0.5</v>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="50">
         <v>1</v>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="51">
         <v>0.6</v>
       </c>
-      <c r="I17" s="51">
+      <c r="I17" s="50">
         <v>1</v>
       </c>
-      <c r="J17" s="52">
+      <c r="J17" s="51">
         <v>0.3</v>
       </c>
-      <c r="K17" s="10"/>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A18" s="10"/>
-      <c r="B18" s="48">
+      <c r="A18" s="9"/>
+      <c r="B18" s="47">
         <v>1392</v>
       </c>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="54" t="s">
+      <c r="D18" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="49">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="48">
         <v>0.5</v>
       </c>
-      <c r="G18" s="51">
+      <c r="G18" s="50">
         <v>1</v>
       </c>
-      <c r="H18" s="52">
+      <c r="H18" s="51">
         <v>0.6</v>
       </c>
-      <c r="I18" s="51">
+      <c r="I18" s="50">
         <v>1</v>
       </c>
-      <c r="J18" s="52">
+      <c r="J18" s="51">
         <v>0.3</v>
       </c>
-      <c r="K18" s="10"/>
+      <c r="K18" s="9"/>
     </row>
     <row r="19" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A19" s="10"/>
-      <c r="B19" s="48">
+      <c r="A19" s="9"/>
+      <c r="B19" s="47">
         <v>1387</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="D19" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="49">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="48">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="50">
         <v>0.01</v>
       </c>
-      <c r="H19" s="52">
+      <c r="H19" s="51">
         <v>0.6</v>
       </c>
-      <c r="I19" s="51">
+      <c r="I19" s="50">
         <v>0.01</v>
       </c>
-      <c r="J19" s="52">
+      <c r="J19" s="51">
         <v>0.3</v>
       </c>
-      <c r="K19" s="10"/>
+      <c r="K19" s="9"/>
     </row>
     <row r="20" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A20" s="10"/>
-      <c r="B20" s="48">
+      <c r="A20" s="9"/>
+      <c r="B20" s="47">
         <v>1386</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="54" t="s">
+      <c r="D20" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="49">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="48">
         <v>0.5</v>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="50">
         <v>1</v>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="51">
         <v>0.6</v>
       </c>
-      <c r="I20" s="51">
+      <c r="I20" s="50">
         <v>1</v>
       </c>
-      <c r="J20" s="52">
+      <c r="J20" s="51">
         <v>0.3</v>
       </c>
-      <c r="K20" s="10"/>
+      <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A21" s="10"/>
-      <c r="B21" s="48">
+      <c r="A21" s="9"/>
+      <c r="B21" s="47">
         <v>1382</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="54" t="s">
+      <c r="D21" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="49">
         <v>2E-3</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="48">
         <v>0.5</v>
       </c>
-      <c r="G21" s="51">
+      <c r="G21" s="50">
         <v>1</v>
       </c>
-      <c r="H21" s="52">
+      <c r="H21" s="51">
         <v>0.6</v>
       </c>
-      <c r="I21" s="51">
+      <c r="I21" s="50">
         <v>1</v>
       </c>
-      <c r="J21" s="52">
+      <c r="J21" s="51">
         <v>0.3</v>
       </c>
-      <c r="K21" s="10"/>
+      <c r="K21" s="9"/>
     </row>
     <row r="22" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A22" s="10"/>
-      <c r="B22" s="48">
+      <c r="A22" s="9"/>
+      <c r="B22" s="47">
         <v>1383</v>
       </c>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="54" t="s">
+      <c r="D22" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="49">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F22" s="48">
         <v>0.5</v>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="50">
         <v>1</v>
       </c>
-      <c r="H22" s="52">
+      <c r="H22" s="51">
         <v>0.6</v>
       </c>
-      <c r="I22" s="51">
+      <c r="I22" s="50">
         <v>1</v>
       </c>
-      <c r="J22" s="52">
+      <c r="J22" s="51">
         <v>0.3</v>
       </c>
-      <c r="K22" s="10"/>
+      <c r="K22" s="9"/>
     </row>
     <row r="23" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A23" s="10"/>
-      <c r="B23" s="48">
+      <c r="A23" s="9"/>
+      <c r="B23" s="47">
         <v>1106</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="54" t="s">
+      <c r="D23" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="49">
         <v>0.01</v>
       </c>
-      <c r="F23" s="49">
+      <c r="F23" s="48">
         <v>0.05</v>
       </c>
-      <c r="G23" s="51">
+      <c r="G23" s="50">
         <v>0.5</v>
       </c>
-      <c r="H23" s="52">
+      <c r="H23" s="51">
         <v>0.6</v>
       </c>
-      <c r="I23" s="51">
+      <c r="I23" s="50">
         <v>0.5</v>
       </c>
-      <c r="J23" s="52">
+      <c r="J23" s="51">
         <v>0.3</v>
       </c>
-      <c r="K23" s="10"/>
+      <c r="K23" s="9"/>
     </row>
     <row r="24" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A24" s="10"/>
-      <c r="B24" s="48">
+      <c r="A24" s="9"/>
+      <c r="B24" s="47">
         <v>1841</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C24" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="D24" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="49">
         <v>0.3</v>
       </c>
-      <c r="F24" s="49">
+      <c r="F24" s="48">
         <v>5</v>
       </c>
-      <c r="G24" s="51">
+      <c r="G24" s="50">
         <v>15</v>
       </c>
-      <c r="H24" s="52">
+      <c r="H24" s="51">
         <v>0.3</v>
       </c>
-      <c r="I24" s="51">
+      <c r="I24" s="50">
         <v>15</v>
       </c>
-      <c r="J24" s="52">
+      <c r="J24" s="51">
         <v>0.1</v>
       </c>
-      <c r="K24" s="10"/>
+      <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11" ht="12.7" x14ac:dyDescent="0.4">
-      <c r="A25" s="10"/>
-      <c r="B25" s="48">
+      <c r="A25" s="9"/>
+      <c r="B25" s="47">
         <v>1798</v>
       </c>
-      <c r="C25" s="48" t="s">
+      <c r="C25" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="54"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="52"/>
-      <c r="K25" s="10"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11" ht="13" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="10"/>
-      <c r="B26" s="55">
+      <c r="A26" s="9"/>
+      <c r="B26" s="54">
         <v>1337</v>
       </c>
-      <c r="C26" s="55" t="s">
+      <c r="C26" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="D26" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="57">
+      <c r="E26" s="56">
         <v>5</v>
       </c>
-      <c r="F26" s="58"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="10"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" ht="13" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="10"/>
-      <c r="B27" s="61">
+      <c r="A27" s="9"/>
+      <c r="B27" s="60">
         <v>1799</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="62" t="s">
+      <c r="D27" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="61"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="65">
+      <c r="E27" s="60"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64">
         <v>0.2</v>
       </c>
-      <c r="I27" s="64"/>
-      <c r="J27" s="65">
+      <c r="I27" s="63"/>
+      <c r="J27" s="64">
         <v>0.05</v>
       </c>
-      <c r="K27" s="11" t="s">
-        <v>71</v>
-      </c>
+      <c r="K27" s="10"/>
     </row>
     <row r="28" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="10"/>
-      <c r="B28" s="128" t="s">
+      <c r="A28" s="9"/>
+      <c r="B28" s="174" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="128"/>
-      <c r="D28" s="128"/>
-      <c r="E28" s="128"/>
-      <c r="F28" s="128"/>
-      <c r="G28" s="128"/>
-      <c r="H28" s="128"/>
-      <c r="I28" s="128"/>
-      <c r="J28" s="128"/>
-      <c r="K28" s="10"/>
+      <c r="C28" s="174"/>
+      <c r="D28" s="174"/>
+      <c r="E28" s="174"/>
+      <c r="F28" s="174"/>
+      <c r="G28" s="174"/>
+      <c r="H28" s="174"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="10"/>
-      <c r="B29" s="128"/>
-      <c r="C29" s="128"/>
-      <c r="D29" s="128"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="128"/>
-      <c r="G29" s="128"/>
-      <c r="H29" s="128"/>
-      <c r="I29" s="128"/>
-      <c r="J29" s="128"/>
-      <c r="K29" s="10"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="174"/>
+      <c r="C29" s="174"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="174"/>
+      <c r="F29" s="174"/>
+      <c r="G29" s="174"/>
+      <c r="H29" s="174"/>
+      <c r="I29" s="174"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="9"/>
     </row>
     <row r="33" spans="4:9" ht="2.1" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="4:9" ht="66.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="37" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D37" s="129"/>
-      <c r="E37" s="130"/>
-      <c r="F37" s="130"/>
-      <c r="G37" s="130"/>
-      <c r="H37" s="130"/>
-      <c r="I37" s="130"/>
+      <c r="D37" s="175"/>
+      <c r="E37" s="176"/>
+      <c r="F37" s="176"/>
+      <c r="G37" s="176"/>
+      <c r="H37" s="176"/>
+      <c r="I37" s="176"/>
     </row>
     <row r="38" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D38" s="130"/>
-      <c r="E38" s="130"/>
-      <c r="F38" s="130"/>
-      <c r="G38" s="130"/>
-      <c r="H38" s="130"/>
-      <c r="I38" s="130"/>
+      <c r="D38" s="176"/>
+      <c r="E38" s="176"/>
+      <c r="F38" s="176"/>
+      <c r="G38" s="176"/>
+      <c r="H38" s="176"/>
+      <c r="I38" s="176"/>
     </row>
     <row r="39" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D39" s="130"/>
-      <c r="E39" s="130"/>
-      <c r="F39" s="130"/>
-      <c r="G39" s="130"/>
-      <c r="H39" s="130"/>
-      <c r="I39" s="130"/>
+      <c r="D39" s="176"/>
+      <c r="E39" s="176"/>
+      <c r="F39" s="176"/>
+      <c r="G39" s="176"/>
+      <c r="H39" s="176"/>
+      <c r="I39" s="176"/>
     </row>
     <row r="40" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D40" s="130"/>
-      <c r="E40" s="130"/>
-      <c r="F40" s="130"/>
-      <c r="G40" s="130"/>
-      <c r="H40" s="130"/>
-      <c r="I40" s="130"/>
+      <c r="D40" s="176"/>
+      <c r="E40" s="176"/>
+      <c r="F40" s="176"/>
+      <c r="G40" s="176"/>
+      <c r="H40" s="176"/>
+      <c r="I40" s="176"/>
     </row>
     <row r="41" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D41" s="130"/>
-      <c r="E41" s="130"/>
-      <c r="F41" s="130"/>
-      <c r="G41" s="130"/>
-      <c r="H41" s="130"/>
-      <c r="I41" s="130"/>
+      <c r="D41" s="176"/>
+      <c r="E41" s="176"/>
+      <c r="F41" s="176"/>
+      <c r="G41" s="176"/>
+      <c r="H41" s="176"/>
+      <c r="I41" s="176"/>
     </row>
     <row r="42" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D42" s="130"/>
-      <c r="E42" s="130"/>
-      <c r="F42" s="130"/>
-      <c r="G42" s="130"/>
-      <c r="H42" s="130"/>
-      <c r="I42" s="130"/>
+      <c r="D42" s="176"/>
+      <c r="E42" s="176"/>
+      <c r="F42" s="176"/>
+      <c r="G42" s="176"/>
+      <c r="H42" s="176"/>
+      <c r="I42" s="176"/>
     </row>
     <row r="43" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D43" s="130"/>
-      <c r="E43" s="130"/>
-      <c r="F43" s="130"/>
-      <c r="G43" s="130"/>
-      <c r="H43" s="130"/>
-      <c r="I43" s="130"/>
+      <c r="D43" s="176"/>
+      <c r="E43" s="176"/>
+      <c r="F43" s="176"/>
+      <c r="G43" s="176"/>
+      <c r="H43" s="176"/>
+      <c r="I43" s="176"/>
     </row>
     <row r="44" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D44" s="130"/>
-      <c r="E44" s="130"/>
-      <c r="F44" s="130"/>
-      <c r="G44" s="130"/>
-      <c r="H44" s="130"/>
-      <c r="I44" s="130"/>
+      <c r="D44" s="176"/>
+      <c r="E44" s="176"/>
+      <c r="F44" s="176"/>
+      <c r="G44" s="176"/>
+      <c r="H44" s="176"/>
+      <c r="I44" s="176"/>
     </row>
     <row r="45" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D45" s="130"/>
-      <c r="E45" s="130"/>
-      <c r="F45" s="130"/>
-      <c r="G45" s="130"/>
-      <c r="H45" s="130"/>
-      <c r="I45" s="130"/>
+      <c r="D45" s="176"/>
+      <c r="E45" s="176"/>
+      <c r="F45" s="176"/>
+      <c r="G45" s="176"/>
+      <c r="H45" s="176"/>
+      <c r="I45" s="176"/>
     </row>
     <row r="46" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D46" s="130"/>
-      <c r="E46" s="130"/>
-      <c r="F46" s="130"/>
-      <c r="G46" s="130"/>
-      <c r="H46" s="130"/>
-      <c r="I46" s="130"/>
+      <c r="D46" s="176"/>
+      <c r="E46" s="176"/>
+      <c r="F46" s="176"/>
+      <c r="G46" s="176"/>
+      <c r="H46" s="176"/>
+      <c r="I46" s="176"/>
     </row>
     <row r="47" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D47" s="130"/>
-      <c r="E47" s="130"/>
-      <c r="F47" s="130"/>
-      <c r="G47" s="130"/>
-      <c r="H47" s="130"/>
-      <c r="I47" s="130"/>
+      <c r="D47" s="176"/>
+      <c r="E47" s="176"/>
+      <c r="F47" s="176"/>
+      <c r="G47" s="176"/>
+      <c r="H47" s="176"/>
+      <c r="I47" s="176"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="JwiDGO3o+2dFxARJYVMUFaBdhSvRBZA582rInYQkmxbsbCPz5oJElMjGmHNl7DdUq/+ISSVBZ98ecfJTPjkUnw==" saltValue="jmeV8ejQYWV9oXQtWWgugQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="3">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B28:J29"/>
@@ -4389,7 +4533,340 @@
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
   <pageSetup paperSize="9" scale="73" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+  <sheetPr codeName="Feuil7"/>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="12.75" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="2.703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5859375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="7" customWidth="1"/>
+    <col min="6" max="6" width="2.703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1171875" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="11" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.41015625" style="1" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="13" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="9"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.7" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="9"/>
+      <c r="B2" s="171" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="12"/>
+    </row>
+    <row r="3" spans="1:6" ht="13" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="51" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="9"/>
+      <c r="B5" s="17">
+        <v>1458</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="20">
+        <v>100</v>
+      </c>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="9"/>
+      <c r="B6" s="21">
+        <v>1114</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="24">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="9"/>
+      <c r="B7" s="21">
+        <v>1115</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="24">
+        <v>100</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="9"/>
+      <c r="B8" s="21">
+        <v>1116</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="24">
+        <v>100</v>
+      </c>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="9"/>
+      <c r="B9" s="21">
+        <v>1117</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="24">
+        <v>100</v>
+      </c>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="9"/>
+      <c r="B10" s="21">
+        <v>1118</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="24">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="9"/>
+      <c r="B11" s="21">
+        <v>6616</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="24">
+        <v>10</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="9"/>
+      <c r="B12" s="21">
+        <v>1497</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="24">
+        <v>10</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="9"/>
+      <c r="B13" s="21">
+        <v>1191</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="24">
+        <v>100</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="9"/>
+      <c r="B14" s="25">
+        <v>1204</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="24">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="9"/>
+      <c r="B15" s="25">
+        <v>1517</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="24">
+        <v>10</v>
+      </c>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="9"/>
+      <c r="B16" s="25">
+        <v>6598</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" s="24">
+        <v>50</v>
+      </c>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="27"/>
+      <c r="B17" s="25">
+        <v>6600</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="24">
+        <v>100</v>
+      </c>
+      <c r="F17" s="27"/>
+    </row>
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="9"/>
+      <c r="B18" s="25">
+        <v>1278</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="24">
+        <v>10</v>
+      </c>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="9"/>
+      <c r="B19" s="25">
+        <v>2879</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" s="24">
+        <v>1000</v>
+      </c>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="9"/>
+      <c r="B20" s="28">
+        <v>1780</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="31">
+        <v>10</v>
+      </c>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" ht="12.7" x14ac:dyDescent="0.4">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="9"/>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="td8wN30mSYRWu68SIYcnfdsAk9EQQuaGdVZDwFc6A+7b+qRG61fZRsb8x7NdEViRu+ic3l+SQ/Fe1k4b/kU7Dw==" saltValue="5H22qEbW9lCx00y8/S02cQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <mergeCells count="1">
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 

--- a/AutosurveillanceTemplates/Comparatif.xlsx
+++ b/AutosurveillanceTemplates/Comparatif.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34A16B1-30EE-496B-8C59-FAFC8ED3D4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EE2D59-09B8-4DD2-8129-1EA5281E59C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-8205" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="SeuilsComparaison-EMT" sheetId="8" r:id="rId2"/>
     <sheet name="LimitequantificationSDE" sheetId="9" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Comparatif!$A$1:$O$35</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
   <si>
     <t>Code SANDRE</t>
   </si>
@@ -325,9 +328,6 @@
     <t xml:space="preserve">Date du comparatif : </t>
   </si>
   <si>
-    <t xml:space="preserve">Le comparatif est-il effectué à partir des prélévements d'une autre station ? </t>
-  </si>
-  <si>
     <t>EMT</t>
   </si>
   <si>
@@ -365,31 +365,39 @@
     <t xml:space="preserve">Nom du(des) laboratoire(s) réalisant les analyses de la matrice eau : </t>
   </si>
   <si>
-    <t xml:space="preserve">Nom du(des) laboratoire(s) réalisant l'analyse de la siccité des boues et des matières séches : </t>
-  </si>
-  <si>
     <t xml:space="preserve">Le(s) laboratoire(s) est/sont-il(s) agréé(s) au titre du code de l’environnement pour l'ensemble des paramètres de la matrice eau résiduaire ? </t>
   </si>
   <si>
     <t xml:space="preserve">A défaut, est ce que le laboratoire réalise un exercice concluant d’intercalibration avec un laboratoire agréé ? </t>
   </si>
   <si>
-    <t>non prise en compte</t>
+    <t xml:space="preserve">Le comparatif est-il effectué à partir des prélèvements d'une autre station ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nom du(des) laboratoire(s) réalisant l'analyse de la siccité des boues et des matières sèches : </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode=";;;"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1441,55 +1449,47 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1497,281 +1497,286 @@
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="3" fontId="15" fillId="5" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="19" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="19" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="7" borderId="29" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="7" borderId="31" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="7" borderId="35" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="7" borderId="29" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="7" borderId="31" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="32" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="7" borderId="35" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="33" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="43" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="7" borderId="46" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="44" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="7" borderId="46" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="7" borderId="25" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="7" borderId="25" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="8" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="8" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="8" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="8" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="8" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="8" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="8" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="8" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1787,116 +1792,119 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1924,20 +1932,20 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1951,10 +1959,10 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1963,37 +1971,37 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2016,10 +2024,10 @@
     <xf numFmtId="10" fontId="0" fillId="13" borderId="42" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2035,13 +2043,13 @@
     <xf numFmtId="10" fontId="0" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2051,35 +2059,44 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2593,23 +2610,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B67ED775-84A5-4DBA-AC81-69F58B98E90C}">
   <sheetPr codeName="Feuil27">
     <tabColor theme="3" tint="0.39997558519241921"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.703125" defaultRowHeight="13" outlineLevelRow="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="13" width="12.703125" style="66" customWidth="1"/>
-    <col min="14" max="14" width="12.703125" style="72" customWidth="1"/>
-    <col min="15" max="15" width="15.64453125" style="72" customWidth="1"/>
-    <col min="16" max="16" width="2.703125" style="66" customWidth="1"/>
-    <col min="17" max="17" width="2.703125" style="65" customWidth="1"/>
-    <col min="18" max="19" width="10.703125" style="65" customWidth="1"/>
-    <col min="20" max="29" width="10.703125" style="65"/>
+    <col min="14" max="14" width="12.703125" style="71" customWidth="1"/>
+    <col min="15" max="15" width="3.703125" style="71" customWidth="1"/>
+    <col min="16" max="16" width="2.703125" style="179" customWidth="1"/>
+    <col min="17" max="17" width="2.703125" style="178" customWidth="1"/>
+    <col min="18" max="19" width="10.703125" style="178" customWidth="1"/>
+    <col min="20" max="24" width="10.703125" style="178"/>
+    <col min="25" max="29" width="10.703125" style="65"/>
     <col min="30" max="16384" width="10.703125" style="66"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A1" s="130" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B1" s="131"/>
       <c r="C1" s="131"/>
@@ -2624,8 +2643,8 @@
       <c r="L1" s="131"/>
       <c r="M1" s="131"/>
       <c r="N1" s="132"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="68"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="177"/>
     </row>
     <row r="2" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A2" s="142" t="s">
@@ -2646,12 +2665,12 @@
       <c r="L2" s="133"/>
       <c r="M2" s="133"/>
       <c r="N2" s="133"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="68"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="177"/>
     </row>
     <row r="3" spans="1:20" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A3" s="107" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B3" s="108"/>
       <c r="C3" s="109"/>
@@ -2660,7 +2679,7 @@
       <c r="F3" s="105"/>
       <c r="G3" s="106"/>
       <c r="H3" s="149" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I3" s="150"/>
       <c r="J3" s="151"/>
@@ -2668,8 +2687,8 @@
       <c r="L3" s="134"/>
       <c r="M3" s="134"/>
       <c r="N3" s="134"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="68"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="177"/>
     </row>
     <row r="4" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8"/>
@@ -2685,109 +2704,109 @@
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="68"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="177"/>
     </row>
     <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="97" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="97"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="177"/>
+    </row>
+    <row r="6" spans="1:20" ht="19.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="98" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
-      <c r="L5" s="98"/>
-      <c r="M5" s="98"/>
-      <c r="N5" s="98"/>
-      <c r="O5" s="76"/>
-      <c r="P5" s="68"/>
-    </row>
-    <row r="6" spans="1:20" ht="19.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="99" t="s">
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="101"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="91"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="75"/>
+      <c r="P6" s="177"/>
+    </row>
+    <row r="7" spans="1:20" ht="19.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="102" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="99"/>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="91"/>
+      <c r="K7" s="91"/>
+      <c r="L7" s="91"/>
+      <c r="M7" s="91"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="177"/>
+    </row>
+    <row r="8" spans="1:20" ht="30.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="100"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="100"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="92"/>
-      <c r="K6" s="92"/>
-      <c r="L6" s="92"/>
-      <c r="M6" s="92"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="68"/>
-    </row>
-    <row r="7" spans="1:20" ht="19.45" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="99" t="s">
+      <c r="B8" s="90"/>
+      <c r="C8" s="90"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="90"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="91"/>
+      <c r="K8" s="91"/>
+      <c r="L8" s="91"/>
+      <c r="M8" s="91"/>
+      <c r="N8" s="92"/>
+      <c r="O8" s="75"/>
+      <c r="P8" s="177"/>
+    </row>
+    <row r="9" spans="1:20" ht="32.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="92"/>
-      <c r="M7" s="92"/>
-      <c r="N7" s="93"/>
-      <c r="O7" s="76"/>
-      <c r="P7" s="68"/>
-    </row>
-    <row r="8" spans="1:20" ht="30.7" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="90" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="91"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="92"/>
-      <c r="K8" s="92"/>
-      <c r="L8" s="92"/>
-      <c r="M8" s="92"/>
-      <c r="N8" s="93"/>
-      <c r="O8" s="76"/>
-      <c r="P8" s="68"/>
-    </row>
-    <row r="9" spans="1:20" ht="32" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="94" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="95"/>
-      <c r="C9" s="95"/>
-      <c r="D9" s="95"/>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="97"/>
-      <c r="O9" s="76"/>
-      <c r="P9" s="68"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="95"/>
+      <c r="K9" s="95"/>
+      <c r="L9" s="95"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="177"/>
     </row>
     <row r="10" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8"/>
@@ -2803,13 +2822,13 @@
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
-      <c r="N10" s="77"/>
-      <c r="O10" s="76"/>
-      <c r="P10" s="68"/>
+      <c r="N10" s="76"/>
+      <c r="O10" s="75"/>
+      <c r="P10" s="177"/>
     </row>
     <row r="11" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A11" s="110" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="111"/>
       <c r="C11" s="111"/>
@@ -2824,8 +2843,8 @@
       <c r="L11" s="111"/>
       <c r="M11" s="111"/>
       <c r="N11" s="112"/>
-      <c r="O11" s="76"/>
-      <c r="P11" s="68"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="177"/>
     </row>
     <row r="12" spans="1:20" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A12" s="126" t="s">
@@ -2836,32 +2855,32 @@
         <v>2</v>
       </c>
       <c r="D12" s="127" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" s="127"/>
       <c r="F12" s="126" t="s">
         <v>3</v>
       </c>
       <c r="G12" s="127" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H12" s="127"/>
       <c r="I12" s="126" t="s">
         <v>3</v>
       </c>
       <c r="J12" s="128" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K12" s="129"/>
       <c r="L12" s="128" t="s">
+        <v>76</v>
+      </c>
+      <c r="M12" s="129"/>
+      <c r="N12" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="M12" s="129"/>
-      <c r="N12" s="78" t="s">
-        <v>78</v>
-      </c>
-      <c r="O12" s="76"/>
-      <c r="P12" s="68"/>
+      <c r="O12" s="75"/>
+      <c r="P12" s="177"/>
     </row>
     <row r="13" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A13" s="126"/>
@@ -2883,23 +2902,23 @@
         <v>0</v>
       </c>
       <c r="M13" s="123"/>
-      <c r="N13" s="84"/>
-      <c r="O13" s="76"/>
-      <c r="P13" s="68"/>
-      <c r="Q13" s="65" t="str">
+      <c r="N13" s="83"/>
+      <c r="O13" s="75"/>
+      <c r="P13" s="177"/>
+      <c r="Q13" s="178" t="str">
         <f>IF(D2&lt;&gt;"",D2,"")</f>
         <v/>
       </c>
-      <c r="R13" s="65" t="str">
+      <c r="R13" s="178" t="str">
         <f>IF(Q13&lt;&gt;"",J13,"")</f>
         <v/>
       </c>
-      <c r="S13" s="65" t="str">
+      <c r="S13" s="178" t="str">
         <f>IF(Q13&lt;&gt;"",L13,"")</f>
         <v/>
       </c>
-      <c r="T13" s="65" t="str">
-        <f>IF(J13&gt;0,100*(L13/J13),"")</f>
+      <c r="T13" s="178" t="str">
+        <f>IF(N13&lt;&gt;"",N13,"")</f>
         <v/>
       </c>
     </row>
@@ -2921,27 +2940,27 @@
         <v>5</v>
       </c>
       <c r="M14" s="125"/>
-      <c r="N14" s="79" t="s">
-        <v>75</v>
-      </c>
-      <c r="O14" s="76"/>
-      <c r="P14" s="68"/>
+      <c r="N14" s="78" t="s">
+        <v>74</v>
+      </c>
+      <c r="O14" s="75"/>
+      <c r="P14" s="177"/>
     </row>
     <row r="15" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A15" s="153" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="153"/>
-      <c r="C15" s="71">
+      <c r="C15" s="70">
         <f>VLOOKUP(A15, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>3</v>
       </c>
       <c r="D15" s="154"/>
       <c r="E15" s="154"/>
-      <c r="F15" s="73"/>
+      <c r="F15" s="72"/>
       <c r="G15" s="154"/>
       <c r="H15" s="154"/>
-      <c r="I15" s="74"/>
+      <c r="I15" s="73"/>
       <c r="J15" s="140" t="str">
         <f>IF(OR(G15="",D15=""),"",IF(ISERROR(VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G15)=TRUE,SUBSTITUTE(G15,"&lt;","",1)*1,G15)&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)-((IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)+IF(ISTEXT(G15)=TRUE,SUBSTITUTE(G15,"&lt;","",1)*1,G15))/2))/((IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)+IF(ISTEXT(G15)=TRUE,SUBSTITUTE(G15,"&lt;","",1),G15))/2),"-")))</f>
         <v/>
@@ -2952,28 +2971,28 @@
         <v/>
       </c>
       <c r="M15" s="139"/>
-      <c r="N15" s="80" t="str">
+      <c r="N15" s="79" t="str">
         <f>IF(OR(AND(ISNUMBER(D15),D15&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G15),G15&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D15,G15)&lt;=VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O15" s="76"/>
-      <c r="P15" s="68"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="177"/>
     </row>
     <row r="16" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A16" s="152" t="s">
         <v>7</v>
       </c>
       <c r="B16" s="152"/>
-      <c r="C16" s="71">
+      <c r="C16" s="70">
         <f>VLOOKUP(A16, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>30</v>
       </c>
       <c r="D16" s="135"/>
       <c r="E16" s="135"/>
-      <c r="F16" s="74"/>
+      <c r="F16" s="73"/>
       <c r="G16" s="135"/>
       <c r="H16" s="135"/>
-      <c r="I16" s="74"/>
+      <c r="I16" s="73"/>
       <c r="J16" s="136" t="str">
         <f>IF(OR(G16="",D16=""),"",IF(ISERROR(VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G16)=TRUE,SUBSTITUTE(G16,"&lt;","",1)*1,G16)&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)-((IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)+IF(ISTEXT(G16)=TRUE,SUBSTITUTE(G16,"&lt;","",1)*1,G16))/2))/((IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)+IF(ISTEXT(G16)=TRUE,SUBSTITUTE(G16,"&lt;","",1),G16))/2),"-")))</f>
         <v/>
@@ -2984,28 +3003,28 @@
         <v/>
       </c>
       <c r="M16" s="139"/>
-      <c r="N16" s="81" t="str">
+      <c r="N16" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D16),D16&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G16),G16&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D16,G16)&lt;=VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O16" s="76"/>
-      <c r="P16" s="68"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="177"/>
     </row>
     <row r="17" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A17" s="152" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="152"/>
-      <c r="C17" s="71">
+      <c r="C17" s="70">
         <f>VLOOKUP(A17, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>10</v>
       </c>
       <c r="D17" s="135"/>
       <c r="E17" s="135"/>
-      <c r="F17" s="74"/>
+      <c r="F17" s="73"/>
       <c r="G17" s="135"/>
       <c r="H17" s="135"/>
-      <c r="I17" s="74"/>
+      <c r="I17" s="73"/>
       <c r="J17" s="136" t="str">
         <f>IF(OR(G17="",D17=""),"",IF(ISERROR(VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G17)=TRUE,SUBSTITUTE(G17,"&lt;","",1)*1,G17)&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)-((IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)+IF(ISTEXT(G17)=TRUE,SUBSTITUTE(G17,"&lt;","",1)*1,G17))/2))/((IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)+IF(ISTEXT(G17)=TRUE,SUBSTITUTE(G17,"&lt;","",1),G17))/2),"-")))</f>
         <v/>
@@ -3016,28 +3035,28 @@
         <v/>
       </c>
       <c r="M17" s="139"/>
-      <c r="N17" s="81" t="str">
+      <c r="N17" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D17),D17&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G17),G17&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D17,G17)&lt;=VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O17" s="76"/>
-      <c r="P17" s="68"/>
+      <c r="O17" s="75"/>
+      <c r="P17" s="177"/>
     </row>
     <row r="18" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A18" s="152" t="s">
         <v>10</v>
       </c>
       <c r="B18" s="152"/>
-      <c r="C18" s="71">
+      <c r="C18" s="70">
         <f>VLOOKUP(A18, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>2</v>
       </c>
       <c r="D18" s="135"/>
       <c r="E18" s="135"/>
-      <c r="F18" s="74"/>
+      <c r="F18" s="73"/>
       <c r="G18" s="135"/>
       <c r="H18" s="135"/>
-      <c r="I18" s="74"/>
+      <c r="I18" s="73"/>
       <c r="J18" s="136" t="str">
         <f>IF(OR(G18="",D18=""),"",IF(ISERROR(VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G18)=TRUE,SUBSTITUTE(G18,"&lt;","",1)*1,G18)&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)-((IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)+IF(ISTEXT(G18)=TRUE,SUBSTITUTE(G18,"&lt;","",1)*1,G18))/2))/((IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)+IF(ISTEXT(G18)=TRUE,SUBSTITUTE(G18,"&lt;","",1),G18))/2),"-")))</f>
         <v/>
@@ -3048,28 +3067,28 @@
         <v/>
       </c>
       <c r="M18" s="139"/>
-      <c r="N18" s="81" t="str">
+      <c r="N18" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D18),D18&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G18),G18&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D18,G18)&lt;=VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O18" s="76"/>
-      <c r="P18" s="68"/>
+      <c r="O18" s="75"/>
+      <c r="P18" s="177"/>
     </row>
     <row r="19" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A19" s="152" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="152"/>
-      <c r="C19" s="71">
+      <c r="C19" s="70">
         <f>VLOOKUP(A19, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0.5</v>
       </c>
       <c r="D19" s="135"/>
       <c r="E19" s="135"/>
-      <c r="F19" s="74"/>
+      <c r="F19" s="73"/>
       <c r="G19" s="135"/>
       <c r="H19" s="135"/>
-      <c r="I19" s="74"/>
+      <c r="I19" s="73"/>
       <c r="J19" s="136" t="str">
         <f>IF(OR(G19="",D19=""),"",IF(ISERROR(VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G19)=TRUE,SUBSTITUTE(G19,"&lt;","",1)*1,G19)&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)-((IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)+IF(ISTEXT(G19)=TRUE,SUBSTITUTE(G19,"&lt;","",1)*1,G19))/2))/((IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)+IF(ISTEXT(G19)=TRUE,SUBSTITUTE(G19,"&lt;","",1),G19))/2),"-")))</f>
         <v/>
@@ -3080,28 +3099,28 @@
         <v/>
       </c>
       <c r="M19" s="139"/>
-      <c r="N19" s="81" t="str">
+      <c r="N19" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D19),D19&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G19),G19&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D19,G19)&lt;=VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O19" s="76"/>
-      <c r="P19" s="68"/>
+      <c r="O19" s="75"/>
+      <c r="P19" s="177"/>
     </row>
     <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A20" s="152" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="152"/>
-      <c r="C20" s="71">
+      <c r="C20" s="70">
         <f>VLOOKUP(A20, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>1</v>
       </c>
       <c r="D20" s="135"/>
       <c r="E20" s="135"/>
-      <c r="F20" s="74"/>
+      <c r="F20" s="73"/>
       <c r="G20" s="135"/>
       <c r="H20" s="135"/>
-      <c r="I20" s="74"/>
+      <c r="I20" s="73"/>
       <c r="J20" s="136" t="str">
         <f>IF(OR(G20="",D20=""),"",IF(ISERROR(VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G20)=TRUE,SUBSTITUTE(G20,"&lt;","",1)*1,G20)&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)-((IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)+IF(ISTEXT(G20)=TRUE,SUBSTITUTE(G20,"&lt;","",1)*1,G20))/2))/((IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)+IF(ISTEXT(G20)=TRUE,SUBSTITUTE(G20,"&lt;","",1),G20))/2),"-")))</f>
         <v/>
@@ -3112,28 +3131,28 @@
         <v/>
       </c>
       <c r="M20" s="139"/>
-      <c r="N20" s="81" t="str">
+      <c r="N20" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D20),D20&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G20),G20&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D20,G20)&lt;=VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O20" s="76"/>
-      <c r="P20" s="68"/>
+      <c r="O20" s="75"/>
+      <c r="P20" s="177"/>
     </row>
     <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A21" s="152" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="152"/>
-      <c r="C21" s="71">
+      <c r="C21" s="70">
         <f>VLOOKUP(A21, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0.5</v>
       </c>
       <c r="D21" s="135"/>
       <c r="E21" s="135"/>
-      <c r="F21" s="74"/>
+      <c r="F21" s="73"/>
       <c r="G21" s="135"/>
       <c r="H21" s="135"/>
-      <c r="I21" s="74"/>
+      <c r="I21" s="73"/>
       <c r="J21" s="136" t="str">
         <f>IF(OR(G21="",D21=""),"",IF(ISERROR(VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G21)=TRUE,SUBSTITUTE(G21,"&lt;","",1)*1,G21)&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)-((IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)+IF(ISTEXT(G21)=TRUE,SUBSTITUTE(G21,"&lt;","",1)*1,G21))/2))/((IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)+IF(ISTEXT(G21)=TRUE,SUBSTITUTE(G21,"&lt;","",1),G21))/2),"-")))</f>
         <v/>
@@ -3144,28 +3163,28 @@
         <v/>
       </c>
       <c r="M21" s="139"/>
-      <c r="N21" s="81" t="str">
+      <c r="N21" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D21),D21&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G21),G21&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D21,G21)&lt;=VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O21" s="76"/>
-      <c r="P21" s="68"/>
+      <c r="O21" s="75"/>
+      <c r="P21" s="177"/>
     </row>
     <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A22" s="152" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="152"/>
-      <c r="C22" s="71">
+      <c r="C22" s="70">
         <f>VLOOKUP(A22, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0.05</v>
       </c>
       <c r="D22" s="135"/>
       <c r="E22" s="135"/>
-      <c r="F22" s="74"/>
+      <c r="F22" s="73"/>
       <c r="G22" s="135"/>
       <c r="H22" s="135"/>
-      <c r="I22" s="74"/>
+      <c r="I22" s="73"/>
       <c r="J22" s="136" t="str">
         <f>IF(OR(G22="",D22=""),"",IF(ISERROR(VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G22)=TRUE,SUBSTITUTE(G22,"&lt;","",1)*1,G22)&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)-((IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)+IF(ISTEXT(G22)=TRUE,SUBSTITUTE(G22,"&lt;","",1)*1,G22))/2))/((IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)+IF(ISTEXT(G22)=TRUE,SUBSTITUTE(G22,"&lt;","",1),G22))/2),"-")))</f>
         <v/>
@@ -3176,28 +3195,28 @@
         <v/>
       </c>
       <c r="M22" s="139"/>
-      <c r="N22" s="81" t="str">
+      <c r="N22" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D22),D22&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G22),G22&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D22,G22)&lt;=VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O22" s="76"/>
-      <c r="P22" s="68"/>
+      <c r="O22" s="75"/>
+      <c r="P22" s="177"/>
     </row>
     <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A23" s="152" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="152"/>
-      <c r="C23" s="71">
+      <c r="C23" s="70">
         <f>VLOOKUP(A23, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>1</v>
       </c>
       <c r="D23" s="135"/>
       <c r="E23" s="135"/>
-      <c r="F23" s="74"/>
+      <c r="F23" s="73"/>
       <c r="G23" s="135"/>
       <c r="H23" s="135"/>
-      <c r="I23" s="74"/>
+      <c r="I23" s="73"/>
       <c r="J23" s="136" t="str">
         <f>IF(OR(G23="",D23=""),"",IF(ISERROR(VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G23)=TRUE,SUBSTITUTE(G23,"&lt;","",1)*1,G23)&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)-((IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)+IF(ISTEXT(G23)=TRUE,SUBSTITUTE(G23,"&lt;","",1)*1,G23))/2))/((IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)+IF(ISTEXT(G23)=TRUE,SUBSTITUTE(G23,"&lt;","",1),G23))/2),"-")))</f>
         <v/>
@@ -3208,28 +3227,28 @@
         <v/>
       </c>
       <c r="M23" s="139"/>
-      <c r="N23" s="81" t="str">
+      <c r="N23" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D23),D23&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G23),G23&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D23,G23)&lt;=VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O23" s="76"/>
-      <c r="P23" s="68"/>
+      <c r="O23" s="75"/>
+      <c r="P23" s="177"/>
     </row>
     <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A24" s="152" t="s">
         <v>16</v>
       </c>
       <c r="B24" s="152"/>
-      <c r="C24" s="71">
+      <c r="C24" s="70">
         <f>VLOOKUP(A24, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0.05</v>
       </c>
       <c r="D24" s="135"/>
       <c r="E24" s="135"/>
-      <c r="F24" s="74"/>
+      <c r="F24" s="73"/>
       <c r="G24" s="135"/>
       <c r="H24" s="135"/>
-      <c r="I24" s="74"/>
+      <c r="I24" s="73"/>
       <c r="J24" s="136" t="str">
         <f>IF(OR(G24="",D24=""),"",IF(ISERROR(VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G24)=TRUE,SUBSTITUTE(G24,"&lt;","",1)*1,G24)&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)-((IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)+IF(ISTEXT(G24)=TRUE,SUBSTITUTE(G24,"&lt;","",1)*1,G24))/2))/((IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)+IF(ISTEXT(G24)=TRUE,SUBSTITUTE(G24,"&lt;","",1),G24))/2),"-")))</f>
         <v/>
@@ -3240,28 +3259,28 @@
         <v/>
       </c>
       <c r="M24" s="139"/>
-      <c r="N24" s="81" t="str">
+      <c r="N24" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D24),D24&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G24),G24&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D24,G24)&lt;=VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O24" s="76"/>
-      <c r="P24" s="68"/>
+      <c r="O24" s="75"/>
+      <c r="P24" s="177"/>
     </row>
     <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A25" s="152" t="s">
         <v>68</v>
       </c>
       <c r="B25" s="152"/>
-      <c r="C25" s="71">
+      <c r="C25" s="70">
         <f>VLOOKUP(A25, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D25" s="155"/>
       <c r="E25" s="155"/>
-      <c r="F25" s="87"/>
+      <c r="F25" s="86"/>
       <c r="G25" s="155"/>
       <c r="H25" s="155"/>
-      <c r="I25" s="87"/>
+      <c r="I25" s="86"/>
       <c r="J25" s="156" t="str">
         <f>IF(OR(G25="",D25=""),"",IF(ISERROR(VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G25)=TRUE,SUBSTITUTE(G25,"&lt;","",1)*1,G25)&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)-((IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)+IF(ISTEXT(G25)=TRUE,SUBSTITUTE(G25,"&lt;","",1)*1,G25))/2))/((IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)+IF(ISTEXT(G25)=TRUE,SUBSTITUTE(G25,"&lt;","",1),G25))/2),"-")))</f>
         <v/>
@@ -3272,14 +3291,12 @@
         <v/>
       </c>
       <c r="M25" s="159"/>
-      <c r="N25" s="81" t="str">
+      <c r="N25" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D25),D25&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G25),G25&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D25,G25)&lt;=VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O25" s="76" t="s">
-        <v>89</v>
-      </c>
-      <c r="P25" s="68"/>
+      <c r="O25" s="75"/>
+      <c r="P25" s="177"/>
     </row>
     <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A26" s="167" t="s">
@@ -3292,10 +3309,10 @@
       </c>
       <c r="D26" s="168"/>
       <c r="E26" s="168"/>
-      <c r="F26" s="88"/>
+      <c r="F26" s="87"/>
       <c r="G26" s="168"/>
       <c r="H26" s="168"/>
-      <c r="I26" s="88"/>
+      <c r="I26" s="87"/>
       <c r="J26" s="156" t="str">
         <f>IF(OR(G26="",D26=""),"",IF(ISERROR(VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G26)=TRUE,SUBSTITUTE(G26,"&lt;","",1)*1,G26)&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)-((IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)+IF(ISTEXT(G26)=TRUE,SUBSTITUTE(G26,"&lt;","",1)*1,G26))/2))/((IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)+IF(ISTEXT(G26)=TRUE,SUBSTITUTE(G26,"&lt;","",1),G26))/2),"-")))</f>
         <v/>
@@ -3306,30 +3323,28 @@
         <v/>
       </c>
       <c r="M26" s="170"/>
-      <c r="N26" s="82" t="str">
+      <c r="N26" s="81" t="str">
         <f>IF(OR(AND(ISNUMBER(D26),D26&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G26),G26&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D26,G26)&lt;=VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O26" s="76" t="s">
-        <v>89</v>
-      </c>
-      <c r="P26" s="68"/>
+      <c r="O26" s="75"/>
+      <c r="P26" s="177"/>
     </row>
     <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A27" s="160" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="160"/>
-      <c r="C27" s="70">
+      <c r="C27" s="69">
         <f>VLOOKUP(A27, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0</v>
       </c>
       <c r="D27" s="161"/>
       <c r="E27" s="161"/>
-      <c r="F27" s="89"/>
+      <c r="F27" s="88"/>
       <c r="G27" s="161"/>
       <c r="H27" s="161"/>
-      <c r="I27" s="89"/>
+      <c r="I27" s="88"/>
       <c r="J27" s="162" t="str">
         <f>IF(OR(G27="",D27=""),"",IF(ISERROR(VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G27)=TRUE,SUBSTITUTE(G27,"&lt;","",1)*1,G27)&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)-((IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)+IF(ISTEXT(G27)=TRUE,SUBSTITUTE(G27,"&lt;","",1)*1,G27))/2))/((IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)+IF(ISTEXT(G27)=TRUE,SUBSTITUTE(G27,"&lt;","",1),G27))/2),"-")))</f>
         <v/>
@@ -3340,14 +3355,12 @@
         <v/>
       </c>
       <c r="M27" s="165"/>
-      <c r="N27" s="83" t="str">
+      <c r="N27" s="82" t="str">
         <f>IF(OR(AND(ISNUMBER(D27),D27&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G27),G27&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D27,G27)&lt;=VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
-      <c r="O27" s="76" t="s">
-        <v>89</v>
-      </c>
-      <c r="P27" s="68"/>
+      <c r="O27" s="75"/>
+      <c r="P27" s="177"/>
     </row>
     <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A28" s="8"/>
@@ -3363,9 +3376,9 @@
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
-      <c r="N28" s="77"/>
-      <c r="O28" s="76"/>
-      <c r="P28" s="68"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="75"/>
+      <c r="P28" s="177"/>
     </row>
     <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A29" s="166" t="s">
@@ -3383,9 +3396,9 @@
       <c r="K29" s="166"/>
       <c r="L29" s="166"/>
       <c r="M29" s="166"/>
-      <c r="N29" s="77"/>
-      <c r="O29" s="76"/>
-      <c r="P29" s="68"/>
+      <c r="N29" s="76"/>
+      <c r="O29" s="75"/>
+      <c r="P29" s="177"/>
     </row>
     <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A30" s="113"/>
@@ -3402,8 +3415,8 @@
       <c r="L30" s="114"/>
       <c r="M30" s="114"/>
       <c r="N30" s="115"/>
-      <c r="O30" s="76"/>
-      <c r="P30" s="68"/>
+      <c r="O30" s="75"/>
+      <c r="P30" s="177"/>
     </row>
     <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A31" s="116"/>
@@ -3420,8 +3433,8 @@
       <c r="L31" s="117"/>
       <c r="M31" s="117"/>
       <c r="N31" s="118"/>
-      <c r="O31" s="76"/>
-      <c r="P31" s="68"/>
+      <c r="O31" s="75"/>
+      <c r="P31" s="177"/>
     </row>
     <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A32" s="116"/>
@@ -3438,8 +3451,8 @@
       <c r="L32" s="117"/>
       <c r="M32" s="117"/>
       <c r="N32" s="118"/>
-      <c r="O32" s="76"/>
-      <c r="P32" s="68"/>
+      <c r="O32" s="75"/>
+      <c r="P32" s="177"/>
     </row>
     <row r="33" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A33" s="116"/>
@@ -3456,8 +3469,8 @@
       <c r="L33" s="117"/>
       <c r="M33" s="117"/>
       <c r="N33" s="118"/>
-      <c r="O33" s="76"/>
-      <c r="P33" s="68"/>
+      <c r="O33" s="75"/>
+      <c r="P33" s="177"/>
     </row>
     <row r="34" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A34" s="119"/>
@@ -3474,29 +3487,29 @@
       <c r="L34" s="120"/>
       <c r="M34" s="120"/>
       <c r="N34" s="121"/>
-      <c r="O34" s="76"/>
-      <c r="P34" s="68"/>
+      <c r="O34" s="75"/>
+      <c r="P34" s="177"/>
     </row>
     <row r="35" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="69"/>
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="69"/>
-      <c r="L35" s="69"/>
-      <c r="M35" s="69"/>
-      <c r="N35" s="75"/>
-      <c r="O35" s="76"/>
-      <c r="P35" s="68"/>
+      <c r="A35" s="68"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="68"/>
+      <c r="I35" s="68"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="68"/>
+      <c r="L35" s="68"/>
+      <c r="M35" s="68"/>
+      <c r="N35" s="74"/>
+      <c r="O35" s="75"/>
+      <c r="P35" s="177"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="E0vgYSLd6IzN3zQpTtpwF407YWeiFI/59Uy/KfslbgamR5SvUT6ebXKuaEoF2kOs5D1P4aRMpT40oh0DZU5zTQ==" saltValue="ZofzeV6n80OCTfHoPp6DgQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="UA120wUyLi6jLGUBrupCpmZ7dF9xVunDXVuc/kAMT1pmWWNdf98MkZMWFnQdA5Mkgce3/dNvfeTxFqRhbCEg3Q==" saltValue="uCr+LukX2ijkiHI3qnzB2A==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="98">
     <mergeCell ref="J24:K24"/>
     <mergeCell ref="A29:M29"/>
@@ -3651,7 +3664,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Coefficient Analytique" prompt="Le coefficient est égale au nombre d'analyse conforme / nombre d'analyse réalisées x le score de pénalité" sqref="N12" xr:uid="{98B0E8A5-51FC-414B-9825-B4FB9B54760B}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="49" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4524,7 +4537,7 @@
       <c r="I47" s="176"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JwiDGO3o+2dFxARJYVMUFaBdhSvRBZA582rInYQkmxbsbCPz5oJElMjGmHNl7DdUq/+ISSVBZ98ecfJTPjkUnw==" saltValue="jmeV8ejQYWV9oXQtWWgugQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="36ILAfe1aRp+IYnRzyNWhOyyc3ulpyDkYQ3G19YLlIXekrnK1Ng6y9L3LrFUIlYT5hEkyhwxGaNLmZ+2dSh+6w==" saltValue="c5XS2WZEVHzEwafG5Pmkfw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="3">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B28:J29"/>
@@ -4860,7 +4873,7 @@
       <c r="F21" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="td8wN30mSYRWu68SIYcnfdsAk9EQQuaGdVZDwFc6A+7b+qRG61fZRsb8x7NdEViRu+ic3l+SQ/Fe1k4b/kU7Dw==" saltValue="5H22qEbW9lCx00y8/S02cQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="g0pkz6+WXI3deDGgoMt+RKzSOF0Qt4U+M+QAWNLAGOjpkVNk12ua6svlmhDoZTt5y3tLXVWHdY21LCdxLS6rng==" saltValue="CjPvU/XsgUWkBHAkGLhuSw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
@@ -4871,6 +4884,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4879,7 +4898,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B79ED2B215C6A64A8EEA6A4A280DADE5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3888bf875947002d9437d5c56d07b5d3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="81251141-7599-4081-9962-8622873f55aa" xmlns:ns3="afd5fb63-b61f-423b-93e7-958e038eacd2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="047a8574d06dd2c3496ab08796c0e7b5" ns2:_="" ns3:_="">
     <xsd:import namespace="81251141-7599-4081-9962-8622873f55aa"/>
@@ -5082,13 +5101,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="81251141-7599-4081-9962-8622873f55aa"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="afd5fb63-b61f-423b-93e7-958e038eacd2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -5096,7 +5126,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2814875-A1EC-46C5-A2DA-1FD958EE2B85}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5113,21 +5143,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="81251141-7599-4081-9962-8622873f55aa"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="afd5fb63-b61f-423b-93e7-958e038eacd2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/AutosurveillanceTemplates/Comparatif.xlsx
+++ b/AutosurveillanceTemplates/Comparatif.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndhuy\AppData\Roaming\Microsoft\AddIns\AutosurveillanceTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EE2D59-09B8-4DD2-8129-1EA5281E59C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54337FAD-E921-4EF7-8272-AAC9E53A53BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-8205" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="887" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1792,54 +1792,146 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="10" fontId="0" fillId="13" borderId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="13" borderId="42" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1932,138 +2024,55 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="13" borderId="49" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="13" borderId="42" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2088,15 +2097,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2618,77 +2618,77 @@
     <col min="1" max="13" width="12.703125" style="66" customWidth="1"/>
     <col min="14" max="14" width="12.703125" style="71" customWidth="1"/>
     <col min="15" max="15" width="3.703125" style="71" customWidth="1"/>
-    <col min="16" max="16" width="2.703125" style="179" customWidth="1"/>
-    <col min="17" max="17" width="2.703125" style="178" customWidth="1"/>
-    <col min="18" max="19" width="10.703125" style="178" customWidth="1"/>
-    <col min="20" max="24" width="10.703125" style="178"/>
+    <col min="16" max="16" width="2.703125" style="91" customWidth="1"/>
+    <col min="17" max="17" width="2.703125" style="90" customWidth="1"/>
+    <col min="18" max="19" width="10.703125" style="90" customWidth="1"/>
+    <col min="20" max="24" width="10.703125" style="90"/>
     <col min="25" max="29" width="10.703125" style="65"/>
     <col min="30" max="16384" width="10.703125" style="66"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="116" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="132"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="117"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="117"/>
+      <c r="M1" s="117"/>
+      <c r="N1" s="118"/>
       <c r="O1" s="75"/>
-      <c r="P1" s="177"/>
+      <c r="P1" s="89"/>
     </row>
     <row r="2" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="142" t="s">
+      <c r="B2" s="124"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="143"/>
-      <c r="J2" s="148"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="133"/>
-      <c r="N2" s="133"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
       <c r="O2" s="75"/>
-      <c r="P2" s="177"/>
+      <c r="P2" s="89"/>
     </row>
     <row r="3" spans="1:20" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="107" t="s">
+      <c r="A3" s="136" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="108"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="149" t="s">
+      <c r="B3" s="137"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="135"/>
+      <c r="H3" s="130" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="150"/>
-      <c r="J3" s="151"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="134"/>
-      <c r="M3" s="134"/>
-      <c r="N3" s="134"/>
+      <c r="I3" s="131"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="120"/>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="120"/>
       <c r="O3" s="75"/>
-      <c r="P3" s="177"/>
+      <c r="P3" s="89"/>
     </row>
     <row r="4" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8"/>
@@ -2706,107 +2706,107 @@
       <c r="M4" s="8"/>
       <c r="N4" s="76"/>
       <c r="O4" s="75"/>
-      <c r="P4" s="177"/>
+      <c r="P4" s="89"/>
     </row>
     <row r="5" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="167" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="97"/>
-      <c r="N5" s="97"/>
+      <c r="B5" s="167"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="167"/>
+      <c r="H5" s="167"/>
+      <c r="I5" s="167"/>
+      <c r="J5" s="167"/>
+      <c r="K5" s="167"/>
+      <c r="L5" s="167"/>
+      <c r="M5" s="167"/>
+      <c r="N5" s="167"/>
       <c r="O5" s="75"/>
-      <c r="P5" s="177"/>
+      <c r="P5" s="89"/>
     </row>
     <row r="6" spans="1:20" ht="19.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="168" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="91"/>
-      <c r="L6" s="91"/>
-      <c r="M6" s="91"/>
-      <c r="N6" s="92"/>
+      <c r="B6" s="169"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="170"/>
+      <c r="H6" s="171"/>
+      <c r="I6" s="161"/>
+      <c r="J6" s="161"/>
+      <c r="K6" s="161"/>
+      <c r="L6" s="161"/>
+      <c r="M6" s="161"/>
+      <c r="N6" s="162"/>
       <c r="O6" s="75"/>
-      <c r="P6" s="177"/>
+      <c r="P6" s="89"/>
     </row>
     <row r="7" spans="1:20" ht="19.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="102" t="s">
+      <c r="A7" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="92"/>
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="173"/>
+      <c r="H7" s="171"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
+      <c r="N7" s="162"/>
       <c r="O7" s="75"/>
-      <c r="P7" s="177"/>
+      <c r="P7" s="89"/>
     </row>
     <row r="8" spans="1:20" ht="30.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="89" t="s">
+      <c r="A8" s="159" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="90"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
+      <c r="B8" s="160"/>
+      <c r="C8" s="160"/>
+      <c r="D8" s="160"/>
+      <c r="E8" s="160"/>
+      <c r="F8" s="160"/>
       <c r="G8" s="84"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="91"/>
-      <c r="J8" s="91"/>
-      <c r="K8" s="91"/>
-      <c r="L8" s="91"/>
-      <c r="M8" s="91"/>
-      <c r="N8" s="92"/>
+      <c r="H8" s="161"/>
+      <c r="I8" s="161"/>
+      <c r="J8" s="161"/>
+      <c r="K8" s="161"/>
+      <c r="L8" s="161"/>
+      <c r="M8" s="161"/>
+      <c r="N8" s="162"/>
       <c r="O8" s="75"/>
-      <c r="P8" s="177"/>
+      <c r="P8" s="89"/>
     </row>
     <row r="9" spans="1:20" ht="32.1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="93" t="s">
+      <c r="A9" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="94"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
+      <c r="B9" s="164"/>
+      <c r="C9" s="164"/>
+      <c r="D9" s="164"/>
+      <c r="E9" s="164"/>
+      <c r="F9" s="164"/>
       <c r="G9" s="85"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="95"/>
-      <c r="K9" s="95"/>
-      <c r="L9" s="95"/>
-      <c r="M9" s="95"/>
-      <c r="N9" s="96"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="165"/>
+      <c r="K9" s="165"/>
+      <c r="L9" s="165"/>
+      <c r="M9" s="165"/>
+      <c r="N9" s="166"/>
       <c r="O9" s="75"/>
-      <c r="P9" s="177"/>
+      <c r="P9" s="89"/>
     </row>
     <row r="10" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8"/>
@@ -2824,543 +2824,543 @@
       <c r="M10" s="8"/>
       <c r="N10" s="76"/>
       <c r="O10" s="75"/>
-      <c r="P10" s="177"/>
+      <c r="P10" s="89"/>
     </row>
     <row r="11" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="110" t="s">
+      <c r="A11" s="139" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="111"/>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
-      <c r="E11" s="111"/>
-      <c r="F11" s="111"/>
-      <c r="G11" s="111"/>
-      <c r="H11" s="111"/>
-      <c r="I11" s="111"/>
-      <c r="J11" s="111"/>
-      <c r="K11" s="111"/>
-      <c r="L11" s="111"/>
-      <c r="M11" s="111"/>
-      <c r="N11" s="112"/>
+      <c r="B11" s="140"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="140"/>
+      <c r="L11" s="140"/>
+      <c r="M11" s="140"/>
+      <c r="N11" s="141"/>
       <c r="O11" s="75"/>
-      <c r="P11" s="177"/>
+      <c r="P11" s="89"/>
     </row>
     <row r="12" spans="1:20" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="126" t="s">
+      <c r="A12" s="155" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="126"/>
-      <c r="C12" s="127" t="s">
+      <c r="B12" s="155"/>
+      <c r="C12" s="156" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="127" t="s">
+      <c r="D12" s="156" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="127"/>
-      <c r="F12" s="126" t="s">
+      <c r="E12" s="156"/>
+      <c r="F12" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="127" t="s">
+      <c r="G12" s="156" t="s">
         <v>82</v>
       </c>
-      <c r="H12" s="127"/>
-      <c r="I12" s="126" t="s">
+      <c r="H12" s="156"/>
+      <c r="I12" s="155" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="128" t="s">
+      <c r="J12" s="157" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="129"/>
-      <c r="L12" s="128" t="s">
+      <c r="K12" s="158"/>
+      <c r="L12" s="157" t="s">
         <v>76</v>
       </c>
-      <c r="M12" s="129"/>
+      <c r="M12" s="158"/>
       <c r="N12" s="77" t="s">
         <v>77</v>
       </c>
       <c r="O12" s="75"/>
-      <c r="P12" s="177"/>
+      <c r="P12" s="89"/>
     </row>
     <row r="13" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="126"/>
-      <c r="B13" s="126"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="126"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="126"/>
-      <c r="J13" s="122">
+      <c r="A13" s="155"/>
+      <c r="B13" s="155"/>
+      <c r="C13" s="156"/>
+      <c r="D13" s="156"/>
+      <c r="E13" s="156"/>
+      <c r="F13" s="155"/>
+      <c r="G13" s="156"/>
+      <c r="H13" s="156"/>
+      <c r="I13" s="155"/>
+      <c r="J13" s="151">
         <f>COUNTA(D15:E24)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="123"/>
-      <c r="L13" s="122">
+      <c r="K13" s="152"/>
+      <c r="L13" s="151">
         <f>COUNTIF(L15:M24,"=Oui")</f>
         <v>0</v>
       </c>
-      <c r="M13" s="123"/>
+      <c r="M13" s="152"/>
       <c r="N13" s="83"/>
       <c r="O13" s="75"/>
-      <c r="P13" s="177"/>
-      <c r="Q13" s="178" t="str">
+      <c r="P13" s="89"/>
+      <c r="Q13" s="90" t="str">
         <f>IF(D2&lt;&gt;"",D2,"")</f>
         <v/>
       </c>
-      <c r="R13" s="178" t="str">
+      <c r="R13" s="90" t="str">
         <f>IF(Q13&lt;&gt;"",J13,"")</f>
         <v/>
       </c>
-      <c r="S13" s="178" t="str">
+      <c r="S13" s="90" t="str">
         <f>IF(Q13&lt;&gt;"",L13,"")</f>
         <v/>
       </c>
-      <c r="T13" s="178" t="str">
+      <c r="T13" s="90" t="str">
         <f>IF(N13&lt;&gt;"",N13,"")</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="126"/>
-      <c r="B14" s="126"/>
-      <c r="C14" s="127"/>
-      <c r="D14" s="127"/>
-      <c r="E14" s="127"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="127"/>
-      <c r="H14" s="127"/>
-      <c r="I14" s="126"/>
-      <c r="J14" s="124" t="s">
+      <c r="A14" s="155"/>
+      <c r="B14" s="155"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
+      <c r="F14" s="155"/>
+      <c r="G14" s="156"/>
+      <c r="H14" s="156"/>
+      <c r="I14" s="155"/>
+      <c r="J14" s="153" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="125"/>
-      <c r="L14" s="124" t="s">
+      <c r="K14" s="154"/>
+      <c r="L14" s="153" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="125"/>
+      <c r="M14" s="154"/>
       <c r="N14" s="78" t="s">
         <v>74</v>
       </c>
       <c r="O14" s="75"/>
-      <c r="P14" s="177"/>
+      <c r="P14" s="89"/>
     </row>
     <row r="15" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="153" t="s">
+      <c r="A15" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="153"/>
+      <c r="B15" s="114"/>
       <c r="C15" s="70">
         <f>VLOOKUP(A15, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>3</v>
       </c>
-      <c r="D15" s="154"/>
-      <c r="E15" s="154"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
       <c r="F15" s="72"/>
-      <c r="G15" s="154"/>
-      <c r="H15" s="154"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
       <c r="I15" s="73"/>
-      <c r="J15" s="140" t="str">
+      <c r="J15" s="121" t="str">
         <f>IF(OR(G15="",D15=""),"",IF(ISERROR(VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G15)=TRUE,SUBSTITUTE(G15,"&lt;","",1)*1,G15)&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)-((IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)+IF(ISTEXT(G15)=TRUE,SUBSTITUTE(G15,"&lt;","",1)*1,G15))/2))/((IF(ISTEXT(D15)=TRUE,SUBSTITUTE(D15,"&lt;","",1)*1,D15)+IF(ISTEXT(G15)=TRUE,SUBSTITUTE(G15,"&lt;","",1),G15))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K15" s="141"/>
-      <c r="L15" s="138" t="str">
+      <c r="K15" s="122"/>
+      <c r="L15" s="95" t="str">
         <f>IF(OR(D15="",G15=""),"",IF(AND(F15="Oui",I15="Oui"),"Oui",IF(J15="-","Oui",IF(OR(G15&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D15&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G15&lt;=VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J15)&lt;=VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J15)&lt;=VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M15" s="139"/>
+      <c r="M15" s="96"/>
       <c r="N15" s="79" t="str">
         <f>IF(OR(AND(ISNUMBER(D15),D15&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G15),G15&gt;VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D15,G15)&lt;=VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A15,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O15" s="75"/>
-      <c r="P15" s="177"/>
+      <c r="P15" s="89"/>
     </row>
     <row r="16" spans="1:20" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="152" t="s">
+      <c r="A16" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="152"/>
+      <c r="B16" s="97"/>
       <c r="C16" s="70">
         <f>VLOOKUP(A16, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>30</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
+      <c r="D16" s="98"/>
+      <c r="E16" s="98"/>
       <c r="F16" s="73"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
+      <c r="G16" s="98"/>
+      <c r="H16" s="98"/>
       <c r="I16" s="73"/>
-      <c r="J16" s="136" t="str">
+      <c r="J16" s="92" t="str">
         <f>IF(OR(G16="",D16=""),"",IF(ISERROR(VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G16)=TRUE,SUBSTITUTE(G16,"&lt;","",1)*1,G16)&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)-((IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)+IF(ISTEXT(G16)=TRUE,SUBSTITUTE(G16,"&lt;","",1)*1,G16))/2))/((IF(ISTEXT(D16)=TRUE,SUBSTITUTE(D16,"&lt;","",1)*1,D16)+IF(ISTEXT(G16)=TRUE,SUBSTITUTE(G16,"&lt;","",1),G16))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K16" s="137"/>
-      <c r="L16" s="138" t="str">
+      <c r="K16" s="93"/>
+      <c r="L16" s="95" t="str">
         <f>IF(OR(D16="",G16=""),"",IF(AND(F16="Oui",I16="Oui"),"Oui",IF(J16="-","Oui",IF(OR(G16&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D16&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G16&lt;=VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J16)&lt;=VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J16)&lt;=VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M16" s="139"/>
+      <c r="M16" s="96"/>
       <c r="N16" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D16),D16&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G16),G16&gt;VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D16,G16)&lt;=VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A16,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O16" s="75"/>
-      <c r="P16" s="177"/>
+      <c r="P16" s="89"/>
     </row>
     <row r="17" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="152" t="s">
+      <c r="A17" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="152"/>
+      <c r="B17" s="97"/>
       <c r="C17" s="70">
         <f>VLOOKUP(A17, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>10</v>
       </c>
-      <c r="D17" s="135"/>
-      <c r="E17" s="135"/>
+      <c r="D17" s="98"/>
+      <c r="E17" s="98"/>
       <c r="F17" s="73"/>
-      <c r="G17" s="135"/>
-      <c r="H17" s="135"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
       <c r="I17" s="73"/>
-      <c r="J17" s="136" t="str">
+      <c r="J17" s="92" t="str">
         <f>IF(OR(G17="",D17=""),"",IF(ISERROR(VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G17)=TRUE,SUBSTITUTE(G17,"&lt;","",1)*1,G17)&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)-((IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)+IF(ISTEXT(G17)=TRUE,SUBSTITUTE(G17,"&lt;","",1)*1,G17))/2))/((IF(ISTEXT(D17)=TRUE,SUBSTITUTE(D17,"&lt;","",1)*1,D17)+IF(ISTEXT(G17)=TRUE,SUBSTITUTE(G17,"&lt;","",1),G17))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K17" s="137"/>
-      <c r="L17" s="138" t="str">
+      <c r="K17" s="93"/>
+      <c r="L17" s="95" t="str">
         <f>IF(OR(D17="",G17=""),"",IF(AND(F17="Oui",I17="Oui"),"Oui",IF(J17="-","Oui",IF(OR(G17&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D17&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G17&lt;=VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J17)&lt;=VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J17)&lt;=VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M17" s="139"/>
+      <c r="M17" s="96"/>
       <c r="N17" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D17),D17&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G17),G17&gt;VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D17,G17)&lt;=VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A17,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O17" s="75"/>
-      <c r="P17" s="177"/>
+      <c r="P17" s="89"/>
     </row>
     <row r="18" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="152" t="s">
+      <c r="A18" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="152"/>
+      <c r="B18" s="97"/>
       <c r="C18" s="70">
         <f>VLOOKUP(A18, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>2</v>
       </c>
-      <c r="D18" s="135"/>
-      <c r="E18" s="135"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="98"/>
       <c r="F18" s="73"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="135"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="98"/>
       <c r="I18" s="73"/>
-      <c r="J18" s="136" t="str">
+      <c r="J18" s="92" t="str">
         <f>IF(OR(G18="",D18=""),"",IF(ISERROR(VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G18)=TRUE,SUBSTITUTE(G18,"&lt;","",1)*1,G18)&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)-((IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)+IF(ISTEXT(G18)=TRUE,SUBSTITUTE(G18,"&lt;","",1)*1,G18))/2))/((IF(ISTEXT(D18)=TRUE,SUBSTITUTE(D18,"&lt;","",1)*1,D18)+IF(ISTEXT(G18)=TRUE,SUBSTITUTE(G18,"&lt;","",1),G18))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K18" s="137"/>
-      <c r="L18" s="138" t="str">
+      <c r="K18" s="93"/>
+      <c r="L18" s="95" t="str">
         <f>IF(OR(D18="",G18=""),"",IF(AND(F18="Oui",I18="Oui"),"Oui",IF(J18="-","Oui",IF(OR(G18&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D18&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G18&lt;=VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J18)&lt;=VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J18)&lt;=VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M18" s="139"/>
+      <c r="M18" s="96"/>
       <c r="N18" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D18),D18&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G18),G18&gt;VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D18,G18)&lt;=VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A18,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O18" s="75"/>
-      <c r="P18" s="177"/>
+      <c r="P18" s="89"/>
     </row>
     <row r="19" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="152" t="s">
+      <c r="A19" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="152"/>
+      <c r="B19" s="97"/>
       <c r="C19" s="70">
         <f>VLOOKUP(A19, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0.5</v>
       </c>
-      <c r="D19" s="135"/>
-      <c r="E19" s="135"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
       <c r="F19" s="73"/>
-      <c r="G19" s="135"/>
-      <c r="H19" s="135"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="98"/>
       <c r="I19" s="73"/>
-      <c r="J19" s="136" t="str">
+      <c r="J19" s="92" t="str">
         <f>IF(OR(G19="",D19=""),"",IF(ISERROR(VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G19)=TRUE,SUBSTITUTE(G19,"&lt;","",1)*1,G19)&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)-((IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)+IF(ISTEXT(G19)=TRUE,SUBSTITUTE(G19,"&lt;","",1)*1,G19))/2))/((IF(ISTEXT(D19)=TRUE,SUBSTITUTE(D19,"&lt;","",1)*1,D19)+IF(ISTEXT(G19)=TRUE,SUBSTITUTE(G19,"&lt;","",1),G19))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K19" s="137"/>
-      <c r="L19" s="138" t="str">
+      <c r="K19" s="93"/>
+      <c r="L19" s="95" t="str">
         <f>IF(OR(D19="",G19=""),"",IF(AND(F19="Oui",I19="Oui"),"Oui",IF(J19="-","Oui",IF(OR(G19&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D19&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G19&lt;=VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J19)&lt;=VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J19)&lt;=VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M19" s="139"/>
+      <c r="M19" s="96"/>
       <c r="N19" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D19),D19&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G19),G19&gt;VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D19,G19)&lt;=VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A19,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O19" s="75"/>
-      <c r="P19" s="177"/>
+      <c r="P19" s="89"/>
     </row>
     <row r="20" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="152" t="s">
+      <c r="A20" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="152"/>
+      <c r="B20" s="97"/>
       <c r="C20" s="70">
         <f>VLOOKUP(A20, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D20" s="135"/>
-      <c r="E20" s="135"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
       <c r="F20" s="73"/>
-      <c r="G20" s="135"/>
-      <c r="H20" s="135"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="98"/>
       <c r="I20" s="73"/>
-      <c r="J20" s="136" t="str">
+      <c r="J20" s="92" t="str">
         <f>IF(OR(G20="",D20=""),"",IF(ISERROR(VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G20)=TRUE,SUBSTITUTE(G20,"&lt;","",1)*1,G20)&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)-((IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)+IF(ISTEXT(G20)=TRUE,SUBSTITUTE(G20,"&lt;","",1)*1,G20))/2))/((IF(ISTEXT(D20)=TRUE,SUBSTITUTE(D20,"&lt;","",1)*1,D20)+IF(ISTEXT(G20)=TRUE,SUBSTITUTE(G20,"&lt;","",1),G20))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K20" s="137"/>
-      <c r="L20" s="138" t="str">
+      <c r="K20" s="93"/>
+      <c r="L20" s="95" t="str">
         <f>IF(OR(D20="",G20=""),"",IF(AND(F20="Oui",I20="Oui"),"Oui",IF(J20="-","Oui",IF(OR(G20&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D20&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G20&lt;=VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J20)&lt;=VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J20)&lt;=VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M20" s="139"/>
+      <c r="M20" s="96"/>
       <c r="N20" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D20),D20&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G20),G20&gt;VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D20,G20)&lt;=VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A20,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O20" s="75"/>
-      <c r="P20" s="177"/>
+      <c r="P20" s="89"/>
     </row>
     <row r="21" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="152" t="s">
+      <c r="A21" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="152"/>
+      <c r="B21" s="97"/>
       <c r="C21" s="70">
         <f>VLOOKUP(A21, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0.5</v>
       </c>
-      <c r="D21" s="135"/>
-      <c r="E21" s="135"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
       <c r="F21" s="73"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="135"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="98"/>
       <c r="I21" s="73"/>
-      <c r="J21" s="136" t="str">
+      <c r="J21" s="92" t="str">
         <f>IF(OR(G21="",D21=""),"",IF(ISERROR(VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G21)=TRUE,SUBSTITUTE(G21,"&lt;","",1)*1,G21)&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)-((IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)+IF(ISTEXT(G21)=TRUE,SUBSTITUTE(G21,"&lt;","",1)*1,G21))/2))/((IF(ISTEXT(D21)=TRUE,SUBSTITUTE(D21,"&lt;","",1)*1,D21)+IF(ISTEXT(G21)=TRUE,SUBSTITUTE(G21,"&lt;","",1),G21))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K21" s="137"/>
-      <c r="L21" s="138" t="str">
+      <c r="K21" s="93"/>
+      <c r="L21" s="95" t="str">
         <f>IF(OR(D21="",G21=""),"",IF(AND(F21="Oui",I21="Oui"),"Oui",IF(J21="-","Oui",IF(OR(G21&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D21&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G21&lt;=VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J21)&lt;=VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J21)&lt;=VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M21" s="139"/>
+      <c r="M21" s="96"/>
       <c r="N21" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D21),D21&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G21),G21&gt;VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D21,G21)&lt;=VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A21,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O21" s="75"/>
-      <c r="P21" s="177"/>
+      <c r="P21" s="89"/>
     </row>
     <row r="22" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="152" t="s">
+      <c r="A22" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="152"/>
+      <c r="B22" s="97"/>
       <c r="C22" s="70">
         <f>VLOOKUP(A22, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0.05</v>
       </c>
-      <c r="D22" s="135"/>
-      <c r="E22" s="135"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="98"/>
       <c r="F22" s="73"/>
-      <c r="G22" s="135"/>
-      <c r="H22" s="135"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="98"/>
       <c r="I22" s="73"/>
-      <c r="J22" s="136" t="str">
+      <c r="J22" s="92" t="str">
         <f>IF(OR(G22="",D22=""),"",IF(ISERROR(VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G22)=TRUE,SUBSTITUTE(G22,"&lt;","",1)*1,G22)&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)-((IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)+IF(ISTEXT(G22)=TRUE,SUBSTITUTE(G22,"&lt;","",1)*1,G22))/2))/((IF(ISTEXT(D22)=TRUE,SUBSTITUTE(D22,"&lt;","",1)*1,D22)+IF(ISTEXT(G22)=TRUE,SUBSTITUTE(G22,"&lt;","",1),G22))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K22" s="137"/>
-      <c r="L22" s="138" t="str">
+      <c r="K22" s="93"/>
+      <c r="L22" s="95" t="str">
         <f>IF(OR(D22="",G22=""),"",IF(AND(F22="Oui",I22="Oui"),"Oui",IF(J22="-","Oui",IF(OR(G22&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D22&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G22&lt;=VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J22)&lt;=VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J22)&lt;=VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M22" s="139"/>
+      <c r="M22" s="96"/>
       <c r="N22" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D22),D22&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G22),G22&gt;VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D22,G22)&lt;=VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A22,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O22" s="75"/>
-      <c r="P22" s="177"/>
+      <c r="P22" s="89"/>
     </row>
     <row r="23" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="152" t="s">
+      <c r="A23" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="152"/>
+      <c r="B23" s="97"/>
       <c r="C23" s="70">
         <f>VLOOKUP(A23, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D23" s="135"/>
-      <c r="E23" s="135"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
       <c r="F23" s="73"/>
-      <c r="G23" s="135"/>
-      <c r="H23" s="135"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="98"/>
       <c r="I23" s="73"/>
-      <c r="J23" s="136" t="str">
+      <c r="J23" s="92" t="str">
         <f>IF(OR(G23="",D23=""),"",IF(ISERROR(VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G23)=TRUE,SUBSTITUTE(G23,"&lt;","",1)*1,G23)&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)-((IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)+IF(ISTEXT(G23)=TRUE,SUBSTITUTE(G23,"&lt;","",1)*1,G23))/2))/((IF(ISTEXT(D23)=TRUE,SUBSTITUTE(D23,"&lt;","",1)*1,D23)+IF(ISTEXT(G23)=TRUE,SUBSTITUTE(G23,"&lt;","",1),G23))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K23" s="137"/>
-      <c r="L23" s="138" t="str">
+      <c r="K23" s="93"/>
+      <c r="L23" s="95" t="str">
         <f>IF(OR(D23="",G23=""),"",IF(AND(F23="Oui",I23="Oui"),"Oui",IF(J23="-","Oui",IF(OR(G23&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D23&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G23&lt;=VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J23)&lt;=VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J23)&lt;=VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M23" s="139"/>
+      <c r="M23" s="96"/>
       <c r="N23" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D23),D23&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G23),G23&gt;VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D23,G23)&lt;=VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A23,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O23" s="75"/>
-      <c r="P23" s="177"/>
+      <c r="P23" s="89"/>
     </row>
     <row r="24" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="152" t="s">
+      <c r="A24" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="152"/>
+      <c r="B24" s="97"/>
       <c r="C24" s="70">
         <f>VLOOKUP(A24, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0.05</v>
       </c>
-      <c r="D24" s="135"/>
-      <c r="E24" s="135"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="98"/>
       <c r="F24" s="73"/>
-      <c r="G24" s="135"/>
-      <c r="H24" s="135"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
       <c r="I24" s="73"/>
-      <c r="J24" s="136" t="str">
+      <c r="J24" s="92" t="str">
         <f>IF(OR(G24="",D24=""),"",IF(ISERROR(VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G24)=TRUE,SUBSTITUTE(G24,"&lt;","",1)*1,G24)&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)-((IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)+IF(ISTEXT(G24)=TRUE,SUBSTITUTE(G24,"&lt;","",1)*1,G24))/2))/((IF(ISTEXT(D24)=TRUE,SUBSTITUTE(D24,"&lt;","",1)*1,D24)+IF(ISTEXT(G24)=TRUE,SUBSTITUTE(G24,"&lt;","",1),G24))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K24" s="137"/>
-      <c r="L24" s="138" t="str">
+      <c r="K24" s="93"/>
+      <c r="L24" s="95" t="str">
         <f>IF(OR(D24="",G24=""),"",IF(AND(F24="Oui",I24="Oui"),"Oui",IF(J24="-","Oui",IF(OR(G24&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D24&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G24&lt;=VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J24)&lt;=VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J24)&lt;=VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M24" s="139"/>
+      <c r="M24" s="96"/>
       <c r="N24" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D24),D24&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G24),G24&gt;VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D24,G24)&lt;=VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A24,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O24" s="75"/>
-      <c r="P24" s="177"/>
+      <c r="P24" s="89"/>
     </row>
     <row r="25" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="152" t="s">
+      <c r="A25" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="152"/>
+      <c r="B25" s="97"/>
       <c r="C25" s="70">
         <f>VLOOKUP(A25, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="155"/>
-      <c r="E25" s="155"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
       <c r="F25" s="86"/>
-      <c r="G25" s="155"/>
-      <c r="H25" s="155"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
       <c r="I25" s="86"/>
-      <c r="J25" s="156" t="str">
+      <c r="J25" s="101" t="str">
         <f>IF(OR(G25="",D25=""),"",IF(ISERROR(VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G25)=TRUE,SUBSTITUTE(G25,"&lt;","",1)*1,G25)&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)-((IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)+IF(ISTEXT(G25)=TRUE,SUBSTITUTE(G25,"&lt;","",1)*1,G25))/2))/((IF(ISTEXT(D25)=TRUE,SUBSTITUTE(D25,"&lt;","",1)*1,D25)+IF(ISTEXT(G25)=TRUE,SUBSTITUTE(G25,"&lt;","",1),G25))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K25" s="157"/>
-      <c r="L25" s="158" t="str">
+      <c r="K25" s="102"/>
+      <c r="L25" s="106" t="str">
         <f>IF(OR(D25="",G25=""),"",IF(AND(F25="Oui",I25="Oui"),"Oui",IF(J25="-","Oui",IF(OR(G25&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D25&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G25&lt;=VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J25)&lt;=VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J25)&lt;=VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M25" s="159"/>
+      <c r="M25" s="107"/>
       <c r="N25" s="80" t="str">
         <f>IF(OR(AND(ISNUMBER(D25),D25&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G25),G25&gt;VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D25,G25)&lt;=VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A25,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O25" s="75"/>
-      <c r="P25" s="177"/>
+      <c r="P25" s="89"/>
     </row>
     <row r="26" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="167" t="s">
+      <c r="A26" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="167"/>
+      <c r="B26" s="99"/>
       <c r="C26" s="67">
         <f>VLOOKUP(A26, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>5</v>
       </c>
-      <c r="D26" s="168"/>
-      <c r="E26" s="168"/>
+      <c r="D26" s="100"/>
+      <c r="E26" s="100"/>
       <c r="F26" s="87"/>
-      <c r="G26" s="168"/>
-      <c r="H26" s="168"/>
+      <c r="G26" s="100"/>
+      <c r="H26" s="100"/>
       <c r="I26" s="87"/>
-      <c r="J26" s="156" t="str">
+      <c r="J26" s="101" t="str">
         <f>IF(OR(G26="",D26=""),"",IF(ISERROR(VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G26)=TRUE,SUBSTITUTE(G26,"&lt;","",1)*1,G26)&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)-((IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)+IF(ISTEXT(G26)=TRUE,SUBSTITUTE(G26,"&lt;","",1)*1,G26))/2))/((IF(ISTEXT(D26)=TRUE,SUBSTITUTE(D26,"&lt;","",1)*1,D26)+IF(ISTEXT(G26)=TRUE,SUBSTITUTE(G26,"&lt;","",1),G26))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K26" s="157"/>
-      <c r="L26" s="169" t="str">
+      <c r="K26" s="102"/>
+      <c r="L26" s="103" t="str">
         <f>IF(OR(D26="",G26=""),"",IF(AND(F26="Oui",I26="Oui"),"Oui",IF(J26="-","Oui",IF(OR(G26&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D26&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G26&lt;=VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J26)&lt;=VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J26)&lt;=VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M26" s="170"/>
+      <c r="M26" s="104"/>
       <c r="N26" s="81" t="str">
         <f>IF(OR(AND(ISNUMBER(D26),D26&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G26),G26&gt;VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D26,G26)&lt;=VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A26,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O26" s="75"/>
-      <c r="P26" s="177"/>
+      <c r="P26" s="89"/>
     </row>
     <row r="27" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="160" t="s">
+      <c r="A27" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="160"/>
+      <c r="B27" s="108"/>
       <c r="C27" s="69">
         <f>VLOOKUP(A27, 'SeuilsComparaison-EMT'!$C$5:$E$28, 3, FALSE)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="161"/>
-      <c r="E27" s="161"/>
+      <c r="D27" s="109"/>
+      <c r="E27" s="109"/>
       <c r="F27" s="88"/>
-      <c r="G27" s="161"/>
-      <c r="H27" s="161"/>
+      <c r="G27" s="109"/>
+      <c r="H27" s="109"/>
       <c r="I27" s="88"/>
-      <c r="J27" s="162" t="str">
+      <c r="J27" s="110" t="str">
         <f>IF(OR(G27="",D27=""),"",IF(ISERROR(VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)),"-",IF(OR(IF(ISTEXT(G27)=TRUE,SUBSTITUTE(G27,"&lt;","",1)*1,G27)&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE),IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$25,4,FALSE)=TRUE),(IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)-((IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)+IF(ISTEXT(G27)=TRUE,SUBSTITUTE(G27,"&lt;","",1)*1,G27))/2))/((IF(ISTEXT(D27)=TRUE,SUBSTITUTE(D27,"&lt;","",1)*1,D27)+IF(ISTEXT(G27)=TRUE,SUBSTITUTE(G27,"&lt;","",1),G27))/2),"-")))</f>
         <v/>
       </c>
-      <c r="K27" s="163"/>
-      <c r="L27" s="164" t="str">
+      <c r="K27" s="111"/>
+      <c r="L27" s="112" t="str">
         <f>IF(OR(D27="",G27=""),"",IF(AND(F27="Oui",I27="Oui"),"Oui",IF(J27="-","Oui",IF(OR(G27&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE),D27&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)=TRUE),IF(G27&lt;=VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),IF(ABS(J27)&lt;=VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),"Oui","Non"),IF(ABS(J27)&lt;=VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE),"Oui","Non")),"Oui"))))</f>
         <v/>
       </c>
-      <c r="M27" s="165"/>
+      <c r="M27" s="113"/>
       <c r="N27" s="82" t="str">
         <f>IF(OR(AND(ISNUMBER(D27),D27&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE)),AND(ISNUMBER(G27),G27&gt;VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,4,FALSE))),IF(AVERAGE(D27,G27)&lt;=VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,5,FALSE),VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,6,FALSE),VLOOKUP(A27,'SeuilsComparaison-EMT'!$C$5:$J$27,8,FALSE)),"")</f>
         <v/>
       </c>
       <c r="O27" s="75"/>
-      <c r="P27" s="177"/>
+      <c r="P27" s="89"/>
     </row>
     <row r="28" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A28" s="8"/>
@@ -3378,117 +3378,117 @@
       <c r="M28" s="8"/>
       <c r="N28" s="76"/>
       <c r="O28" s="75"/>
-      <c r="P28" s="177"/>
+      <c r="P28" s="89"/>
     </row>
     <row r="29" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="166" t="s">
+      <c r="A29" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="166"/>
-      <c r="C29" s="166"/>
-      <c r="D29" s="166"/>
-      <c r="E29" s="166"/>
-      <c r="F29" s="166"/>
-      <c r="G29" s="166"/>
-      <c r="H29" s="166"/>
-      <c r="I29" s="166"/>
-      <c r="J29" s="166"/>
-      <c r="K29" s="166"/>
-      <c r="L29" s="166"/>
-      <c r="M29" s="166"/>
+      <c r="B29" s="94"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="94"/>
+      <c r="E29" s="94"/>
+      <c r="F29" s="94"/>
+      <c r="G29" s="94"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="94"/>
+      <c r="K29" s="94"/>
+      <c r="L29" s="94"/>
+      <c r="M29" s="94"/>
       <c r="N29" s="76"/>
       <c r="O29" s="75"/>
-      <c r="P29" s="177"/>
+      <c r="P29" s="89"/>
     </row>
     <row r="30" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="113"/>
-      <c r="B30" s="114"/>
-      <c r="C30" s="114"/>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="114"/>
-      <c r="I30" s="114"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="114"/>
-      <c r="L30" s="114"/>
-      <c r="M30" s="114"/>
-      <c r="N30" s="115"/>
+      <c r="A30" s="142"/>
+      <c r="B30" s="143"/>
+      <c r="C30" s="143"/>
+      <c r="D30" s="143"/>
+      <c r="E30" s="143"/>
+      <c r="F30" s="143"/>
+      <c r="G30" s="143"/>
+      <c r="H30" s="143"/>
+      <c r="I30" s="143"/>
+      <c r="J30" s="143"/>
+      <c r="K30" s="143"/>
+      <c r="L30" s="143"/>
+      <c r="M30" s="143"/>
+      <c r="N30" s="144"/>
       <c r="O30" s="75"/>
-      <c r="P30" s="177"/>
+      <c r="P30" s="89"/>
     </row>
     <row r="31" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="116"/>
-      <c r="B31" s="117"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="117"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="117"/>
-      <c r="H31" s="117"/>
-      <c r="I31" s="117"/>
-      <c r="J31" s="117"/>
-      <c r="K31" s="117"/>
-      <c r="L31" s="117"/>
-      <c r="M31" s="117"/>
-      <c r="N31" s="118"/>
+      <c r="A31" s="145"/>
+      <c r="B31" s="146"/>
+      <c r="C31" s="146"/>
+      <c r="D31" s="146"/>
+      <c r="E31" s="146"/>
+      <c r="F31" s="146"/>
+      <c r="G31" s="146"/>
+      <c r="H31" s="146"/>
+      <c r="I31" s="146"/>
+      <c r="J31" s="146"/>
+      <c r="K31" s="146"/>
+      <c r="L31" s="146"/>
+      <c r="M31" s="146"/>
+      <c r="N31" s="147"/>
       <c r="O31" s="75"/>
-      <c r="P31" s="177"/>
+      <c r="P31" s="89"/>
     </row>
     <row r="32" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="116"/>
-      <c r="B32" s="117"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="117"/>
-      <c r="I32" s="117"/>
-      <c r="J32" s="117"/>
-      <c r="K32" s="117"/>
-      <c r="L32" s="117"/>
-      <c r="M32" s="117"/>
-      <c r="N32" s="118"/>
+      <c r="A32" s="145"/>
+      <c r="B32" s="146"/>
+      <c r="C32" s="146"/>
+      <c r="D32" s="146"/>
+      <c r="E32" s="146"/>
+      <c r="F32" s="146"/>
+      <c r="G32" s="146"/>
+      <c r="H32" s="146"/>
+      <c r="I32" s="146"/>
+      <c r="J32" s="146"/>
+      <c r="K32" s="146"/>
+      <c r="L32" s="146"/>
+      <c r="M32" s="146"/>
+      <c r="N32" s="147"/>
       <c r="O32" s="75"/>
-      <c r="P32" s="177"/>
+      <c r="P32" s="89"/>
     </row>
     <row r="33" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="116"/>
-      <c r="B33" s="117"/>
-      <c r="C33" s="117"/>
-      <c r="D33" s="117"/>
-      <c r="E33" s="117"/>
-      <c r="F33" s="117"/>
-      <c r="G33" s="117"/>
-      <c r="H33" s="117"/>
-      <c r="I33" s="117"/>
-      <c r="J33" s="117"/>
-      <c r="K33" s="117"/>
-      <c r="L33" s="117"/>
-      <c r="M33" s="117"/>
-      <c r="N33" s="118"/>
+      <c r="A33" s="145"/>
+      <c r="B33" s="146"/>
+      <c r="C33" s="146"/>
+      <c r="D33" s="146"/>
+      <c r="E33" s="146"/>
+      <c r="F33" s="146"/>
+      <c r="G33" s="146"/>
+      <c r="H33" s="146"/>
+      <c r="I33" s="146"/>
+      <c r="J33" s="146"/>
+      <c r="K33" s="146"/>
+      <c r="L33" s="146"/>
+      <c r="M33" s="146"/>
+      <c r="N33" s="147"/>
       <c r="O33" s="75"/>
-      <c r="P33" s="177"/>
+      <c r="P33" s="89"/>
     </row>
     <row r="34" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="119"/>
-      <c r="B34" s="120"/>
-      <c r="C34" s="120"/>
-      <c r="D34" s="120"/>
-      <c r="E34" s="120"/>
-      <c r="F34" s="120"/>
-      <c r="G34" s="120"/>
-      <c r="H34" s="120"/>
-      <c r="I34" s="120"/>
-      <c r="J34" s="120"/>
-      <c r="K34" s="120"/>
-      <c r="L34" s="120"/>
-      <c r="M34" s="120"/>
-      <c r="N34" s="121"/>
+      <c r="A34" s="148"/>
+      <c r="B34" s="149"/>
+      <c r="C34" s="149"/>
+      <c r="D34" s="149"/>
+      <c r="E34" s="149"/>
+      <c r="F34" s="149"/>
+      <c r="G34" s="149"/>
+      <c r="H34" s="149"/>
+      <c r="I34" s="149"/>
+      <c r="J34" s="149"/>
+      <c r="K34" s="149"/>
+      <c r="L34" s="149"/>
+      <c r="M34" s="149"/>
+      <c r="N34" s="150"/>
       <c r="O34" s="75"/>
-      <c r="P34" s="177"/>
+      <c r="P34" s="89"/>
     </row>
     <row r="35" spans="1:16" ht="20.100000000000001" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.4">
       <c r="A35" s="68"/>
@@ -3506,11 +3506,93 @@
       <c r="M35" s="68"/>
       <c r="N35" s="74"/>
       <c r="O35" s="75"/>
-      <c r="P35" s="177"/>
+      <c r="P35" s="89"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="UA120wUyLi6jLGUBrupCpmZ7dF9xVunDXVuc/kAMT1pmWWNdf98MkZMWFnQdA5Mkgce3/dNvfeTxFqRhbCEg3Q==" saltValue="uCr+LukX2ijkiHI3qnzB2A==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="2HywmHFFIkFp8n3OYqDWc3F9/4bqtDnzFT6ertEFv6wNgqIWY8q9k+DnIaZwQkDq8ZZmdsHtaN/aesConDYrkg==" saltValue="zkpqxP7W6c1nhMBlDwLLBQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="98">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A30:N34"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="A12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="G12:H14"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
     <mergeCell ref="J24:K24"/>
     <mergeCell ref="A29:M29"/>
     <mergeCell ref="J19:K19"/>
@@ -3527,88 +3609,6 @@
     <mergeCell ref="J26:K26"/>
     <mergeCell ref="L26:M26"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K3:N3"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="A30:N34"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="A12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:E14"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="G12:H14"/>
-    <mergeCell ref="I12:I14"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="H7:N7"/>
   </mergeCells>
   <conditionalFormatting sqref="A9:N9">
     <cfRule type="expression" dxfId="8" priority="1">
@@ -3704,17 +3704,17 @@
     </row>
     <row r="2" spans="1:11" ht="15.7" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9"/>
-      <c r="B2" s="171" t="s">
+      <c r="B2" s="174" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
-      <c r="J2" s="173"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
+      <c r="J2" s="176"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="13" thickBot="1" x14ac:dyDescent="0.45">
@@ -4420,124 +4420,124 @@
     </row>
     <row r="28" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="9"/>
-      <c r="B28" s="174" t="s">
+      <c r="B28" s="177" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="174"/>
-      <c r="D28" s="174"/>
-      <c r="E28" s="174"/>
-      <c r="F28" s="174"/>
-      <c r="G28" s="174"/>
-      <c r="H28" s="174"/>
-      <c r="I28" s="174"/>
-      <c r="J28" s="174"/>
+      <c r="C28" s="177"/>
+      <c r="D28" s="177"/>
+      <c r="E28" s="177"/>
+      <c r="F28" s="177"/>
+      <c r="G28" s="177"/>
+      <c r="H28" s="177"/>
+      <c r="I28" s="177"/>
+      <c r="J28" s="177"/>
       <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" ht="14.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="9"/>
-      <c r="B29" s="174"/>
-      <c r="C29" s="174"/>
-      <c r="D29" s="174"/>
-      <c r="E29" s="174"/>
-      <c r="F29" s="174"/>
-      <c r="G29" s="174"/>
-      <c r="H29" s="174"/>
-      <c r="I29" s="174"/>
-      <c r="J29" s="174"/>
+      <c r="B29" s="177"/>
+      <c r="C29" s="177"/>
+      <c r="D29" s="177"/>
+      <c r="E29" s="177"/>
+      <c r="F29" s="177"/>
+      <c r="G29" s="177"/>
+      <c r="H29" s="177"/>
+      <c r="I29" s="177"/>
+      <c r="J29" s="177"/>
       <c r="K29" s="9"/>
     </row>
     <row r="33" spans="4:9" ht="2.1" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="34" spans="4:9" ht="66.75" hidden="1" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="37" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D37" s="175"/>
-      <c r="E37" s="176"/>
-      <c r="F37" s="176"/>
-      <c r="G37" s="176"/>
-      <c r="H37" s="176"/>
-      <c r="I37" s="176"/>
+      <c r="D37" s="178"/>
+      <c r="E37" s="179"/>
+      <c r="F37" s="179"/>
+      <c r="G37" s="179"/>
+      <c r="H37" s="179"/>
+      <c r="I37" s="179"/>
     </row>
     <row r="38" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D38" s="176"/>
-      <c r="E38" s="176"/>
-      <c r="F38" s="176"/>
-      <c r="G38" s="176"/>
-      <c r="H38" s="176"/>
-      <c r="I38" s="176"/>
+      <c r="D38" s="179"/>
+      <c r="E38" s="179"/>
+      <c r="F38" s="179"/>
+      <c r="G38" s="179"/>
+      <c r="H38" s="179"/>
+      <c r="I38" s="179"/>
     </row>
     <row r="39" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D39" s="176"/>
-      <c r="E39" s="176"/>
-      <c r="F39" s="176"/>
-      <c r="G39" s="176"/>
-      <c r="H39" s="176"/>
-      <c r="I39" s="176"/>
+      <c r="D39" s="179"/>
+      <c r="E39" s="179"/>
+      <c r="F39" s="179"/>
+      <c r="G39" s="179"/>
+      <c r="H39" s="179"/>
+      <c r="I39" s="179"/>
     </row>
     <row r="40" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D40" s="176"/>
-      <c r="E40" s="176"/>
-      <c r="F40" s="176"/>
-      <c r="G40" s="176"/>
-      <c r="H40" s="176"/>
-      <c r="I40" s="176"/>
+      <c r="D40" s="179"/>
+      <c r="E40" s="179"/>
+      <c r="F40" s="179"/>
+      <c r="G40" s="179"/>
+      <c r="H40" s="179"/>
+      <c r="I40" s="179"/>
     </row>
     <row r="41" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D41" s="176"/>
-      <c r="E41" s="176"/>
-      <c r="F41" s="176"/>
-      <c r="G41" s="176"/>
-      <c r="H41" s="176"/>
-      <c r="I41" s="176"/>
+      <c r="D41" s="179"/>
+      <c r="E41" s="179"/>
+      <c r="F41" s="179"/>
+      <c r="G41" s="179"/>
+      <c r="H41" s="179"/>
+      <c r="I41" s="179"/>
     </row>
     <row r="42" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D42" s="176"/>
-      <c r="E42" s="176"/>
-      <c r="F42" s="176"/>
-      <c r="G42" s="176"/>
-      <c r="H42" s="176"/>
-      <c r="I42" s="176"/>
+      <c r="D42" s="179"/>
+      <c r="E42" s="179"/>
+      <c r="F42" s="179"/>
+      <c r="G42" s="179"/>
+      <c r="H42" s="179"/>
+      <c r="I42" s="179"/>
     </row>
     <row r="43" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D43" s="176"/>
-      <c r="E43" s="176"/>
-      <c r="F43" s="176"/>
-      <c r="G43" s="176"/>
-      <c r="H43" s="176"/>
-      <c r="I43" s="176"/>
+      <c r="D43" s="179"/>
+      <c r="E43" s="179"/>
+      <c r="F43" s="179"/>
+      <c r="G43" s="179"/>
+      <c r="H43" s="179"/>
+      <c r="I43" s="179"/>
     </row>
     <row r="44" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D44" s="176"/>
-      <c r="E44" s="176"/>
-      <c r="F44" s="176"/>
-      <c r="G44" s="176"/>
-      <c r="H44" s="176"/>
-      <c r="I44" s="176"/>
+      <c r="D44" s="179"/>
+      <c r="E44" s="179"/>
+      <c r="F44" s="179"/>
+      <c r="G44" s="179"/>
+      <c r="H44" s="179"/>
+      <c r="I44" s="179"/>
     </row>
     <row r="45" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D45" s="176"/>
-      <c r="E45" s="176"/>
-      <c r="F45" s="176"/>
-      <c r="G45" s="176"/>
-      <c r="H45" s="176"/>
-      <c r="I45" s="176"/>
+      <c r="D45" s="179"/>
+      <c r="E45" s="179"/>
+      <c r="F45" s="179"/>
+      <c r="G45" s="179"/>
+      <c r="H45" s="179"/>
+      <c r="I45" s="179"/>
     </row>
     <row r="46" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D46" s="176"/>
-      <c r="E46" s="176"/>
-      <c r="F46" s="176"/>
-      <c r="G46" s="176"/>
-      <c r="H46" s="176"/>
-      <c r="I46" s="176"/>
+      <c r="D46" s="179"/>
+      <c r="E46" s="179"/>
+      <c r="F46" s="179"/>
+      <c r="G46" s="179"/>
+      <c r="H46" s="179"/>
+      <c r="I46" s="179"/>
     </row>
     <row r="47" spans="4:9" ht="12.7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="D47" s="176"/>
-      <c r="E47" s="176"/>
-      <c r="F47" s="176"/>
-      <c r="G47" s="176"/>
-      <c r="H47" s="176"/>
-      <c r="I47" s="176"/>
+      <c r="D47" s="179"/>
+      <c r="E47" s="179"/>
+      <c r="F47" s="179"/>
+      <c r="G47" s="179"/>
+      <c r="H47" s="179"/>
+      <c r="I47" s="179"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="36ILAfe1aRp+IYnRzyNWhOyyc3ulpyDkYQ3G19YLlIXekrnK1Ng6y9L3LrFUIlYT5hEkyhwxGaNLmZ+2dSh+6w==" saltValue="c5XS2WZEVHzEwafG5Pmkfw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="V3qDv/3oSCVYiSTrRObq3Fy7+HwdpakZzuxlOp9wPfeigSpEUE67uu53qPnhx77TJGMlfcrs4ahGEgbk6GpN4Q==" saltValue="g/a60fUq0JwAw75jBpCgCQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="3">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B28:J29"/>
@@ -4576,12 +4576,12 @@
     </row>
     <row r="2" spans="1:6" ht="15.7" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9"/>
-      <c r="B2" s="171" t="s">
+      <c r="B2" s="174" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="173"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="176"/>
       <c r="F2" s="12"/>
     </row>
     <row r="3" spans="1:6" ht="13" thickBot="1" x14ac:dyDescent="0.45">
@@ -4873,7 +4873,7 @@
       <c r="F21" s="9"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="g0pkz6+WXI3deDGgoMt+RKzSOF0Qt4U+M+QAWNLAGOjpkVNk12ua6svlmhDoZTt5y3tLXVWHdY21LCdxLS6rng==" saltValue="CjPvU/XsgUWkBHAkGLhuSw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="V0QIXJcMDgrIN3onuxiIFLO0ueAtpP6GPYHaKUtUpcIfjxMGlMpKeSr6tvsbcT53gqKdtaC9INsQ7MEN206XGA==" saltValue="2BussPIHdpdOnSPUV366dw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatRows="0"/>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
@@ -4884,21 +4884,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B79ED2B215C6A64A8EEA6A4A280DADE5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3888bf875947002d9437d5c56d07b5d3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="81251141-7599-4081-9962-8622873f55aa" xmlns:ns3="afd5fb63-b61f-423b-93e7-958e038eacd2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="047a8574d06dd2c3496ab08796c0e7b5" ns2:_="" ns3:_="">
     <xsd:import namespace="81251141-7599-4081-9962-8622873f55aa"/>
@@ -5101,32 +5086,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="81251141-7599-4081-9962-8622873f55aa"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="afd5fb63-b61f-423b-93e7-958e038eacd2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2814875-A1EC-46C5-A2DA-1FD958EE2B85}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5143,4 +5118,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB702087-7E88-4AF3-B693-D27B95F8995C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA52DDF1-DB9E-4C0C-9E16-F265EDFF44E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="81251141-7599-4081-9962-8622873f55aa"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="afd5fb63-b61f-423b-93e7-958e038eacd2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>